--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -45,19 +45,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,6 +93,156 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -87,37 +261,1489 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,175 +1755,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF3BAF55"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,1477 +1767,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF3BAF55"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF9DD6AA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1791,37 +1839,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA1D8AE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1833,25 +1851,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5257,40 +5257,40 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="2">
         <v>10.01</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="8">
         <v>17.19</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="9">
         <v>5.47</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="3">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="4">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="5">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="11">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="6">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="12">
         <v>-16.59</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="1">
         <v>-38.96</v>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5319,40 +5319,40 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>7.24</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="17">
         <v>4.08</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="14">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="15">
         <v>0.96</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="18">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="19">
         <v>-11</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="23">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="24">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="26">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="25">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="20">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="21">
         <v>-19.16</v>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,40 +5381,40 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="37">
         <v>0</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="39">
         <v>0.15</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="27">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="28">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="32">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="33">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="29">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="30">
         <v>-23.39</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="34">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="35">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="31">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="36">
         <v>-22.78</v>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="48" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5443,40 +5443,40 @@
       <c r="H5">
         <v>-2.91</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="43">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="49">
         <v>1.94</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="50">
         <v>4</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="45">
         <v>4.69</v>
       </c>
       <c r="M5" s="42">
         <v>11.75</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="44">
         <v>4.44</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="51">
         <v>6.5</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="46">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="52">
         <v>2</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="47">
         <v>12.19</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="40">
         <v>20.06</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="41">
         <v>32</v>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5508,37 +5508,37 @@
       <c r="I6" s="59">
         <v>9.1</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="60">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="61">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="64">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="55">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="53">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="62">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="56">
         <v>-18.71</v>
       </c>
       <c r="Q6" s="57">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="65">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="58">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="54">
         <v>-38.6</v>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,40 +5567,40 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="78">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="74">
         <v>0.95</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="75">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="71">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="76">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="73">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="72">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="77">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="66">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="67">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="68">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="69">
         <v>-30.62</v>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="81" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,40 +5629,40 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="86">
         <v>3.82</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="87">
         <v>14.19</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="82">
         <v>25.58</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="88">
         <v>38.12</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="90">
         <v>24.33</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="79">
         <v>11.91</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="83">
         <v>0.74</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="84">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="80">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="85">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="89">
         <v>-10.43</v>
       </c>
-      <c r="T8" s="85">
+      <c r="T8" s="91">
         <v>39.26</v>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="95" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,34 +5691,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="96">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="97">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="98">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="101">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="92">
         <v>-36.12</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="93">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="100">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="99">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="99">
+      <c r="T9" s="94">
         <v>-37.12</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="103" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5747,32 +5747,32 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="104">
+      <c r="I10" s="103">
         <v>-2.09</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="110">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="106">
         <v>-6</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="107">
         <v>-8.64</v>
       </c>
       <c r="M10" s="102">
         <v>-9.74</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="108">
         <v>-8.97</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="104">
         <v>-10.07</v>
       </c>
       <c r="P10" t="str"/>
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="109">
+      <c r="T10" s="105">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="112" t="str">
+      <c r="D11" s="122" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,40 +5801,40 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="118">
         <v>0</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="123">
         <v>10</v>
       </c>
-      <c r="K11" s="117">
+      <c r="K11" s="115">
         <v>21</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="111">
         <v>33.11</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="112">
         <v>24.68</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="121">
         <v>37.11</v>
       </c>
-      <c r="O11" s="111">
+      <c r="O11" s="116">
         <v>50.84</v>
       </c>
-      <c r="P11" s="113">
+      <c r="P11" s="119">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="114">
+      <c r="Q11" s="113">
         <v>77.16</v>
       </c>
-      <c r="R11" s="115">
+      <c r="R11" s="120">
         <v>59.42</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="114">
         <v>50.05</v>
       </c>
-      <c r="T11" s="116">
+      <c r="T11" s="117">
         <v>59.47</v>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="134" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5863,40 +5863,40 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="129">
+      <c r="I12" s="135">
         <v>8.55</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="127">
         <v>19.41</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="131">
         <v>11.85</v>
       </c>
-      <c r="L12" s="124">
+      <c r="L12" s="130">
         <v>22.99</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="136">
         <v>35.32</v>
       </c>
-      <c r="N12" s="125">
+      <c r="N12" s="132">
         <v>44.48</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="128">
         <v>58.92</v>
       </c>
-      <c r="P12" s="126">
+      <c r="P12" s="133">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="127">
+      <c r="Q12" s="124">
         <v>34.61</v>
       </c>
-      <c r="R12" s="128">
+      <c r="R12" s="129">
         <v>45.23</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="125">
         <v>42.21</v>
       </c>
-      <c r="T12" s="130">
+      <c r="T12" s="126">
         <v>43.06</v>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="143" t="str">
+      <c r="D13" s="147" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5925,37 +5925,37 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="148">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="137">
+      <c r="J13" s="140">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="138">
+      <c r="K13" s="144">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="140">
+      <c r="L13" s="141">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="149">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="142">
         <v>-1.22</v>
       </c>
       <c r="O13" s="145">
         <v>-4.31</v>
       </c>
-      <c r="P13" s="141">
+      <c r="P13" s="139">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="142">
+      <c r="Q13" s="143">
         <v>33.43</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="137">
         <v>31.11</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="138">
         <v>64.98</v>
       </c>
       <c r="T13" s="146">
@@ -5972,7 +5972,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="150" t="str">
+      <c r="D14" s="156" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -5987,31 +5987,31 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="153">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="151">
+      <c r="J14" s="159">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="155">
+      <c r="K14" s="160">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="150">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="154">
         <v>4.78</v>
       </c>
-      <c r="N14" s="152">
+      <c r="N14" s="161">
         <v>1.5</v>
       </c>
-      <c r="O14" s="153">
+      <c r="O14" s="151">
         <v>27.74</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="152">
         <v>41.52</v>
       </c>
-      <c r="Q14" s="156">
+      <c r="Q14" s="155">
         <v>39.07</v>
       </c>
       <c r="R14" s="162">
@@ -6020,7 +6020,7 @@
       <c r="S14" s="157">
         <v>60.1</v>
       </c>
-      <c r="T14" s="154">
+      <c r="T14" s="158">
         <v>15.04</v>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="167" t="str">
+      <c r="D15" s="166" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,13 +6049,13 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="168">
+      <c r="I15" s="171">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="165">
+      <c r="J15" s="172">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="166">
+      <c r="K15" s="173">
         <v>-2.7</v>
       </c>
       <c r="L15" s="169">
@@ -6067,22 +6067,22 @@
       <c r="N15" s="175">
         <v>30.65</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="167">
         <v>44.75</v>
       </c>
-      <c r="P15" s="163">
+      <c r="P15" s="164">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="170">
         <v>78.98</v>
       </c>
-      <c r="R15" s="164">
+      <c r="R15" s="165">
         <v>63.75</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="168">
         <v>56.8</v>
       </c>
-      <c r="T15" s="173">
+      <c r="T15" s="163">
         <v>17.66</v>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="182" t="str">
+      <c r="D16" s="181" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6111,40 +6111,40 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="177">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="187">
         <v>-4.7</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="188">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="182">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="176">
+      <c r="M16" s="186">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="178">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="177">
+      <c r="O16" s="179">
         <v>8.25</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="176">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="180">
+      <c r="Q16" s="183">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="178">
+      <c r="R16" s="180">
         <v>-5.62</v>
       </c>
-      <c r="S16" s="181">
+      <c r="S16" s="184">
         <v>9.38</v>
       </c>
-      <c r="T16" s="179">
+      <c r="T16" s="185">
         <v>-24.96</v>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="198" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,40 +6173,40 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="191">
         <v>3.38</v>
       </c>
-      <c r="J17" s="197">
+      <c r="J17" s="195">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="189">
+      <c r="K17" s="192">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="190">
+      <c r="L17" s="196">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="192">
+      <c r="M17" s="193">
         <v>2.69</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="197">
         <v>17.43</v>
       </c>
-      <c r="O17" s="191">
+      <c r="O17" s="199">
         <v>21.27</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="189">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="193">
+      <c r="Q17" s="190">
         <v>2.39</v>
       </c>
-      <c r="R17" s="194">
+      <c r="R17" s="200">
         <v>18.66</v>
       </c>
-      <c r="S17" s="195">
+      <c r="S17" s="201">
         <v>13.27</v>
       </c>
-      <c r="T17" s="196">
+      <c r="T17" s="194">
         <v>-18.6</v>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="202" t="str">
+      <c r="D18" s="210" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,37 +6235,37 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="207">
+      <c r="I18" s="202">
         <v>0</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="214">
         <v>9.99</v>
       </c>
       <c r="K18" s="211">
         <v>20.99</v>
       </c>
-      <c r="L18" s="208">
+      <c r="L18" s="203">
         <v>33.11</v>
       </c>
-      <c r="M18" s="203">
+      <c r="M18" s="212">
         <v>19.81</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="204">
         <v>7.83</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="213">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="204">
+      <c r="P18" s="205">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="207">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="208">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="205">
+      <c r="S18" s="209">
         <v>-14.75</v>
       </c>
       <c r="T18" s="206">
@@ -6282,7 +6282,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="220" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,40 +6297,40 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="221">
+      <c r="I19" s="223">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="215">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="217">
         <v>-7.41</v>
       </c>
       <c r="L19" s="224">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="215">
+      <c r="M19" s="227">
         <v>-9.01</v>
       </c>
       <c r="N19" s="216">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="218">
         <v>-8.21</v>
       </c>
-      <c r="P19" s="217">
+      <c r="P19" s="219">
         <v>-11.42</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="225">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="220">
         <v>-11.35</v>
       </c>
-      <c r="S19" s="219">
+      <c r="S19" s="221">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="227">
+      <c r="T19" s="222">
         <v>-22.3</v>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="236" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6359,40 +6359,40 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="228">
+      <c r="I20" s="232">
         <v>3.51</v>
       </c>
       <c r="J20" s="229">
         <v>10.28</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="237">
         <v>2.56</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="239">
         <v>11.62</v>
       </c>
-      <c r="M20" s="230">
+      <c r="M20" s="238">
         <v>10.45</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="233">
         <v>8.02</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="230">
         <v>8.38</v>
       </c>
-      <c r="P20" s="233">
+      <c r="P20" s="240">
         <v>0.96</v>
       </c>
       <c r="Q20" s="234">
         <v>1.95</v>
       </c>
-      <c r="R20" s="231">
+      <c r="R20" s="228">
         <v>28.49</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="231">
         <v>20.94</v>
       </c>
-      <c r="T20" s="232">
+      <c r="T20" s="235">
         <v>20.38</v>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="242" t="str">
+      <c r="D21" s="249" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6421,40 +6421,40 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="243">
+      <c r="I21" s="250">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="251">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="246">
+      <c r="K21" s="253">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="241">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="252">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="242">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="244">
+      <c r="O21" s="245">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="247">
+      <c r="P21" s="246">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="247">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="245">
+      <c r="R21" s="243">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="244">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="241">
+      <c r="T21" s="248">
         <v>-22.05</v>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="258" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6486,37 +6486,37 @@
       <c r="I22" s="255">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="256">
+      <c r="J22" s="264">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="257">
+      <c r="K22" s="265">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="258">
+      <c r="L22" s="259">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="256">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="260">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="259">
+      <c r="O22" s="261">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="263">
         <v>-29.39</v>
       </c>
       <c r="Q22" s="266">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="260">
+      <c r="R22" s="262">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="254">
+      <c r="S22" s="257">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="261">
+      <c r="T22" s="254">
         <v>-32.26</v>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="273" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6545,40 +6545,40 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="277">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="267">
+      <c r="J23" s="278">
         <v>-9.06</v>
       </c>
-      <c r="K23" s="271">
+      <c r="K23" s="279">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="272">
+      <c r="L23" s="271">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="274">
+      <c r="M23" s="267">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="268">
+      <c r="N23" s="274">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="268">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="273">
+      <c r="P23" s="272">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="269">
+      <c r="Q23" s="275">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="270">
+      <c r="R23" s="269">
         <v>-10.32</v>
       </c>
       <c r="S23" s="276">
         <v>-9.91</v>
       </c>
-      <c r="T23" s="277">
+      <c r="T23" s="270">
         <v>-3.14</v>
       </c>
     </row>
@@ -6641,40 +6641,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="287">
+      <c r="I25" s="285">
         <v>27.27</v>
       </c>
-      <c r="J25" s="289">
+      <c r="J25" s="291">
         <v>45.45</v>
       </c>
-      <c r="K25" s="281">
+      <c r="K25" s="286">
         <v>31.82</v>
       </c>
-      <c r="L25" s="282">
+      <c r="L25" s="290">
         <v>40.91</v>
       </c>
-      <c r="M25" s="290">
+      <c r="M25" s="280">
         <v>40.91</v>
       </c>
-      <c r="N25" s="291">
+      <c r="N25" s="287">
         <v>40.91</v>
       </c>
-      <c r="O25" s="283">
+      <c r="O25" s="282">
         <v>40.91</v>
       </c>
-      <c r="P25" s="288">
+      <c r="P25" s="281">
         <v>47.62</v>
       </c>
-      <c r="Q25" s="284">
+      <c r="Q25" s="283">
         <v>40</v>
       </c>
-      <c r="R25" s="285">
+      <c r="R25" s="288">
         <v>40</v>
       </c>
-      <c r="S25" s="280">
+      <c r="S25" s="289">
         <v>45</v>
       </c>
-      <c r="T25" s="286">
+      <c r="T25" s="284">
         <v>36.36</v>
       </c>
     </row>
@@ -6689,37 +6689,37 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="299">
+      <c r="I26" s="302">
         <v>-1.94</v>
       </c>
-      <c r="J26" s="300">
+      <c r="J26" s="301">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="295">
+      <c r="K26" s="299">
         <v>-1.81</v>
       </c>
-      <c r="L26" s="292">
+      <c r="L26" s="300">
         <v>-0.48</v>
       </c>
-      <c r="M26" s="296">
+      <c r="M26" s="295">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="301">
+      <c r="N26" s="303">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="302">
+      <c r="O26" s="296">
         <v>1.67</v>
       </c>
-      <c r="P26" s="303">
+      <c r="P26" s="292">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="297">
+      <c r="Q26" s="293">
         <v>4.66</v>
       </c>
-      <c r="R26" s="293">
+      <c r="R26" s="294">
         <v>7.06</v>
       </c>
-      <c r="S26" s="294">
+      <c r="S26" s="297">
         <v>7.81</v>
       </c>
       <c r="T26" s="298">

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -45,7 +45,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,6 +117,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -81,13 +225,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,25 +255,241 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,13 +501,1225 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,175 +1731,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,127 +1749,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -459,1327 +1785,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1797,13 +1809,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1816,42 +1852,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5242,7 +5242,7 @@
       <c r="C2" t="str">
         <v>605398</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="7" t="str">
         <v>净买: 309.39万</v>
       </c>
       <c r="E2">
@@ -5257,40 +5257,40 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="8">
         <v>10.01</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="10">
         <v>17.19</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="4">
         <v>5.47</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="12">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="13">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="9">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="1">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="5">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="6">
         <v>-16.59</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="2">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="3">
         <v>-38.96</v>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5319,40 +5319,40 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="26">
         <v>7.24</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="20">
         <v>4.08</v>
       </c>
       <c r="K3" s="14">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="17">
         <v>0.96</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="23">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="21">
         <v>-11</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="18">
         <v>-8.43</v>
       </c>
       <c r="P3" s="24">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="15">
         <v>-16.36</v>
       </c>
       <c r="R3" s="25">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="22">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="19">
         <v>-19.16</v>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,40 +5381,40 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="31">
         <v>0</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="37">
         <v>0.15</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="38">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="33">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="34">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="35">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="28">
         <v>-23.39</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="39">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="27">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="29">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="30">
         <v>-22.78</v>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5443,40 +5443,40 @@
       <c r="H5">
         <v>-2.91</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="50">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="47">
         <v>1.94</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="48">
         <v>4</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="44">
         <v>4.69</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="41">
         <v>11.75</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="51">
         <v>4.44</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="45">
         <v>6.5</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="42">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="43">
         <v>2</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="52">
         <v>12.19</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="49">
         <v>20.06</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="46">
         <v>32</v>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5505,40 +5505,40 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="60">
         <v>9.1</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="62">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="54">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="55">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="56">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="64">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="57">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="58">
         <v>-18.71</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="63">
         <v>-17.67</v>
       </c>
       <c r="R6" s="65">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="59">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="61">
         <v>-38.6</v>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,40 +5567,40 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="68">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="77">
         <v>0.95</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="69">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="75">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="70">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="78">
         <v>-8.15</v>
       </c>
       <c r="O7" s="72">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="73">
         <v>-8.22</v>
       </c>
       <c r="Q7" s="66">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="76">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="67">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="69">
+      <c r="T7" s="71">
         <v>-30.62</v>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="86" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,40 +5629,40 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="87">
         <v>3.82</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="88">
         <v>14.19</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="91">
         <v>25.58</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="84">
         <v>38.12</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="82">
         <v>24.33</v>
       </c>
       <c r="N8" s="79">
         <v>11.91</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="80">
         <v>0.74</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="89">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="90">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="81">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="85">
         <v>-10.43</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="83">
         <v>39.26</v>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="96" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,34 +5691,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="99">
         <v>-26.15</v>
       </c>
       <c r="J9" s="97">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="94">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="100">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="101">
         <v>-36.12</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="92">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="93">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="98">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="94">
+      <c r="T9" s="95">
         <v>-37.12</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="106" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5753,26 +5753,26 @@
       <c r="J10" s="110">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="104">
         <v>-6</v>
       </c>
       <c r="L10" s="107">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="105">
         <v>-9.74</v>
       </c>
       <c r="N10" s="108">
         <v>-8.97</v>
       </c>
-      <c r="O10" s="104">
+      <c r="O10" s="109">
         <v>-10.07</v>
       </c>
       <c r="P10" t="str"/>
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="105">
+      <c r="T10" s="102">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="112" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,40 +5801,40 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="111">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="113">
         <v>10</v>
       </c>
-      <c r="K11" s="115">
+      <c r="K11" s="114">
         <v>21</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="119">
         <v>33.11</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="120">
         <v>24.68</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="115">
         <v>37.11</v>
       </c>
-      <c r="O11" s="116">
+      <c r="O11" s="121">
         <v>50.84</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="116">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="113">
+      <c r="Q11" s="117">
         <v>77.16</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="122">
         <v>59.42</v>
       </c>
-      <c r="S11" s="114">
+      <c r="S11" s="123">
         <v>50.05</v>
       </c>
-      <c r="T11" s="117">
+      <c r="T11" s="118">
         <v>59.47</v>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5863,40 +5863,40 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="127">
         <v>8.55</v>
       </c>
-      <c r="J12" s="127">
+      <c r="J12" s="125">
         <v>19.41</v>
       </c>
       <c r="K12" s="131">
         <v>11.85</v>
       </c>
-      <c r="L12" s="130">
+      <c r="L12" s="128">
         <v>22.99</v>
       </c>
       <c r="M12" s="136">
         <v>35.32</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="124">
         <v>44.48</v>
       </c>
-      <c r="O12" s="128">
+      <c r="O12" s="132">
         <v>58.92</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="129">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="124">
+      <c r="Q12" s="133">
         <v>34.61</v>
       </c>
-      <c r="R12" s="129">
+      <c r="R12" s="134">
         <v>45.23</v>
       </c>
-      <c r="S12" s="125">
+      <c r="S12" s="126">
         <v>42.21</v>
       </c>
-      <c r="T12" s="126">
+      <c r="T12" s="130">
         <v>43.06</v>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="140" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5925,40 +5925,40 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="149">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="140">
+      <c r="J13" s="145">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="138">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="137">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="141">
         <v>-10.31</v>
       </c>
       <c r="N13" s="142">
         <v>-1.22</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="146">
         <v>-4.31</v>
       </c>
       <c r="P13" s="139">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="143">
+      <c r="Q13" s="147">
         <v>33.43</v>
       </c>
-      <c r="R13" s="137">
+      <c r="R13" s="148">
         <v>31.11</v>
       </c>
-      <c r="S13" s="138">
+      <c r="S13" s="143">
         <v>64.98</v>
       </c>
-      <c r="T13" s="146">
+      <c r="T13" s="144">
         <v>8.46</v>
       </c>
     </row>
@@ -5987,40 +5987,40 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="153">
+      <c r="I14" s="157">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="162">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="153">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="150">
+      <c r="L14" s="154">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="154">
+      <c r="M14" s="150">
         <v>4.78</v>
       </c>
-      <c r="N14" s="161">
+      <c r="N14" s="151">
         <v>1.5</v>
       </c>
-      <c r="O14" s="151">
+      <c r="O14" s="155">
         <v>27.74</v>
       </c>
-      <c r="P14" s="152">
+      <c r="P14" s="158">
         <v>41.52</v>
       </c>
-      <c r="Q14" s="155">
+      <c r="Q14" s="152">
         <v>39.07</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="159">
         <v>75</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="160">
         <v>60.1</v>
       </c>
-      <c r="T14" s="158">
+      <c r="T14" s="161">
         <v>15.04</v>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="166" t="str">
+      <c r="D15" s="164" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,37 +6049,37 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="165">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="171">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="175">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="169">
+      <c r="L15" s="172">
         <v>7.16</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="167">
         <v>3.81</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="168">
         <v>30.65</v>
       </c>
-      <c r="O15" s="167">
+      <c r="O15" s="173">
         <v>44.75</v>
       </c>
-      <c r="P15" s="164">
+      <c r="P15" s="174">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="169">
         <v>78.98</v>
       </c>
-      <c r="R15" s="165">
+      <c r="R15" s="170">
         <v>63.75</v>
       </c>
-      <c r="S15" s="168">
+      <c r="S15" s="166">
         <v>56.8</v>
       </c>
       <c r="T15" s="163">
@@ -6096,7 +6096,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="181" t="str">
+      <c r="D16" s="178" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6111,34 +6111,34 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="179">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="182">
         <v>-4.7</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="183">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="182">
+      <c r="L16" s="176">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="180">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="178">
+      <c r="N16" s="186">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="179">
+      <c r="O16" s="177">
         <v>8.25</v>
       </c>
-      <c r="P16" s="176">
+      <c r="P16" s="187">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="188">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="180">
+      <c r="R16" s="181">
         <v>-5.62</v>
       </c>
       <c r="S16" s="184">
@@ -6158,7 +6158,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="189" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,40 +6173,40 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="191">
+      <c r="I17" s="190">
         <v>3.38</v>
       </c>
-      <c r="J17" s="195">
+      <c r="J17" s="194">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="192">
+      <c r="K17" s="198">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="191">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="193">
+      <c r="M17" s="199">
         <v>2.69</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="192">
         <v>17.43</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="193">
         <v>21.27</v>
       </c>
-      <c r="P17" s="189">
+      <c r="P17" s="195">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="190">
+      <c r="Q17" s="200">
         <v>2.39</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="196">
         <v>18.66</v>
       </c>
       <c r="S17" s="201">
         <v>13.27</v>
       </c>
-      <c r="T17" s="194">
+      <c r="T17" s="197">
         <v>-18.6</v>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="209" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,40 +6235,40 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="202">
+      <c r="I18" s="206">
         <v>0</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="210">
         <v>9.99</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="202">
         <v>20.99</v>
       </c>
       <c r="L18" s="203">
         <v>33.11</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="211">
         <v>19.81</v>
       </c>
       <c r="N18" s="204">
         <v>7.83</v>
       </c>
-      <c r="O18" s="213">
+      <c r="O18" s="207">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="205">
+      <c r="P18" s="214">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="207">
+      <c r="Q18" s="205">
         <v>-13.43</v>
       </c>
       <c r="R18" s="208">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="212">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="206">
+      <c r="T18" s="213">
         <v>-28.01</v>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,40 +6297,40 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="220">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="223">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="217">
+      <c r="K19" s="224">
         <v>-7.41</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="225">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="226">
         <v>-9.01</v>
       </c>
-      <c r="N19" s="216">
+      <c r="N19" s="227">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="218">
+      <c r="O19" s="216">
         <v>-8.21</v>
       </c>
-      <c r="P19" s="219">
+      <c r="P19" s="217">
         <v>-11.42</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="218">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="220">
+      <c r="R19" s="219">
         <v>-11.35</v>
       </c>
       <c r="S19" s="221">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="222">
+      <c r="T19" s="215">
         <v>-22.3</v>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="236" t="str">
+      <c r="D20" s="231" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6359,40 +6359,40 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="232">
+      <c r="I20" s="237">
         <v>3.51</v>
       </c>
-      <c r="J20" s="229">
+      <c r="J20" s="228">
         <v>10.28</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="234">
         <v>2.56</v>
       </c>
-      <c r="L20" s="239">
+      <c r="L20" s="229">
         <v>11.62</v>
       </c>
       <c r="M20" s="238">
         <v>10.45</v>
       </c>
-      <c r="N20" s="233">
+      <c r="N20" s="239">
         <v>8.02</v>
       </c>
       <c r="O20" s="230">
         <v>8.38</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="232">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="234">
+      <c r="Q20" s="235">
         <v>1.95</v>
       </c>
-      <c r="R20" s="228">
+      <c r="R20" s="240">
         <v>28.49</v>
       </c>
-      <c r="S20" s="231">
+      <c r="S20" s="236">
         <v>20.94</v>
       </c>
-      <c r="T20" s="235">
+      <c r="T20" s="233">
         <v>20.38</v>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="249" t="str">
+      <c r="D21" s="250" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6421,40 +6421,40 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="243">
         <v>-13.19</v>
       </c>
       <c r="J21" s="251">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="253">
+      <c r="K21" s="252">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="241">
+      <c r="L21" s="253">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="244">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="242">
+      <c r="N21" s="241">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="245">
+      <c r="O21" s="246">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="246">
+      <c r="P21" s="247">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="247">
+      <c r="Q21" s="249">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="243">
+      <c r="R21" s="248">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="244">
+      <c r="S21" s="242">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="248">
+      <c r="T21" s="245">
         <v>-22.05</v>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="258" t="str">
+      <c r="D22" s="263" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6483,40 +6483,40 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="255">
+      <c r="I22" s="261">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="264">
+      <c r="J22" s="258">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="254">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="259">
+      <c r="L22" s="264">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="256">
+      <c r="M22" s="262">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="260">
+      <c r="N22" s="265">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="255">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="263">
+      <c r="P22" s="266">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="256">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="259">
         <v>-33.76</v>
       </c>
       <c r="S22" s="257">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="254">
+      <c r="T22" s="260">
         <v>-32.26</v>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="273" t="str">
+      <c r="D23" s="276" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6548,37 +6548,37 @@
       <c r="I23" s="277">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="272">
         <v>-9.06</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="268">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="271">
+      <c r="L23" s="278">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="267">
+      <c r="M23" s="279">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="269">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="268">
+      <c r="O23" s="273">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="272">
+      <c r="P23" s="274">
         <v>-11.69</v>
       </c>
       <c r="Q23" s="275">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="269">
+      <c r="R23" s="267">
         <v>-10.32</v>
       </c>
-      <c r="S23" s="276">
+      <c r="S23" s="270">
         <v>-9.91</v>
       </c>
-      <c r="T23" s="270">
+      <c r="T23" s="271">
         <v>-3.14</v>
       </c>
     </row>
@@ -6641,40 +6641,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="285">
+      <c r="I25" s="280">
         <v>27.27</v>
       </c>
-      <c r="J25" s="291">
+      <c r="J25" s="286">
         <v>45.45</v>
       </c>
-      <c r="K25" s="286">
+      <c r="K25" s="282">
         <v>31.82</v>
       </c>
-      <c r="L25" s="290">
+      <c r="L25" s="283">
         <v>40.91</v>
       </c>
-      <c r="M25" s="280">
+      <c r="M25" s="287">
         <v>40.91</v>
       </c>
-      <c r="N25" s="287">
+      <c r="N25" s="284">
         <v>40.91</v>
       </c>
-      <c r="O25" s="282">
+      <c r="O25" s="288">
         <v>40.91</v>
       </c>
-      <c r="P25" s="281">
+      <c r="P25" s="289">
         <v>47.62</v>
       </c>
-      <c r="Q25" s="283">
+      <c r="Q25" s="291">
         <v>40</v>
       </c>
-      <c r="R25" s="288">
+      <c r="R25" s="285">
         <v>40</v>
       </c>
-      <c r="S25" s="289">
+      <c r="S25" s="281">
         <v>45</v>
       </c>
-      <c r="T25" s="284">
+      <c r="T25" s="290">
         <v>36.36</v>
       </c>
     </row>
@@ -6689,37 +6689,37 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="302">
+      <c r="I26" s="299">
         <v>-1.94</v>
       </c>
-      <c r="J26" s="301">
+      <c r="J26" s="296">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="299">
+      <c r="K26" s="297">
         <v>-1.81</v>
       </c>
       <c r="L26" s="300">
         <v>-0.48</v>
       </c>
-      <c r="M26" s="295">
+      <c r="M26" s="293">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="303">
+      <c r="N26" s="301">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="296">
+      <c r="O26" s="302">
         <v>1.67</v>
       </c>
-      <c r="P26" s="292">
+      <c r="P26" s="294">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="293">
+      <c r="Q26" s="295">
         <v>4.66</v>
       </c>
-      <c r="R26" s="294">
+      <c r="R26" s="292">
         <v>7.06</v>
       </c>
-      <c r="S26" s="297">
+      <c r="S26" s="303">
         <v>7.81</v>
       </c>
       <c r="T26" s="298">

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -57,13 +57,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD73242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,19 +129,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,24 +231,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -135,37 +243,1531 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF8D8DB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7E35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,1549 +1779,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1731,108 +1839,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA1D8AE"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCBE9D2"/>
         <bgColor/>
       </patternFill>
@@ -1840,18 +1852,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5242,7 +5242,7 @@
       <c r="C2" t="str">
         <v>605398</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 309.39万</v>
       </c>
       <c r="E2">
@@ -5257,41 +5257,41 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>0</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="11">
         <v>10.01</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="6">
         <v>17.19</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="10">
         <v>5.47</v>
       </c>
       <c r="M2" s="12">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="1">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="7">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="8">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="2">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="3">
         <v>-16.59</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="4">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="3">
-        <v>-38.96</v>
+      <c r="T2" s="9">
+        <v>-38.87</v>
       </c>
     </row>
     <row r="3">
@@ -5304,7 +5304,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5319,41 +5319,41 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <v>7.24</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="19">
         <v>4.08</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="21">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="25">
         <v>0.96</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="16">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="22">
         <v>-11</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="17">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="20">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="26">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="18">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="14">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="19">
-        <v>-19.16</v>
+      <c r="T3" s="23">
+        <v>-17.42</v>
       </c>
     </row>
     <row r="4">
@@ -5366,7 +5366,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,41 +5381,41 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="32">
         <v>0</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="35">
         <v>0.15</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="27">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="28">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="36">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="37">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="33">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="29">
         <v>-23.39</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="30">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="38">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="39">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="30">
-        <v>-22.78</v>
+      <c r="T4" s="31">
+        <v>-22.93</v>
       </c>
     </row>
     <row r="5">
@@ -5428,7 +5428,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="50" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5443,41 +5443,41 @@
       <c r="H5">
         <v>-2.91</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="51">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="52">
         <v>1.94</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="43">
         <v>4</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="46">
         <v>4.69</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="44">
         <v>11.75</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="49">
         <v>4.44</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="47">
         <v>6.5</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="45">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="48">
         <v>2</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="40">
         <v>12.19</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="41">
         <v>20.06</v>
       </c>
-      <c r="T5" s="46">
-        <v>32</v>
+      <c r="T5" s="42">
+        <v>33.31</v>
       </c>
     </row>
     <row r="6">
@@ -5490,7 +5490,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="54" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5505,41 +5505,41 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="55">
         <v>9.1</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="65">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="59">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="56">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="53">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="57">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="61">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="62">
         <v>-18.71</v>
       </c>
       <c r="Q6" s="63">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="60">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="58">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="61">
-        <v>-38.6</v>
+      <c r="T6" s="64">
+        <v>-37.56</v>
       </c>
     </row>
     <row r="7">
@@ -5552,7 +5552,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,41 +5567,41 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="73">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="78">
         <v>0.95</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="68">
         <v>-2.72</v>
       </c>
       <c r="L7" s="75">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="69">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="66">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="70">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="71">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="76">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="77">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="72">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="71">
-        <v>-30.62</v>
+      <c r="T7" s="74">
+        <v>-29.44</v>
       </c>
     </row>
     <row r="8">
@@ -5614,7 +5614,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,41 +5629,41 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="88">
         <v>3.82</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="89">
         <v>14.19</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="80">
         <v>25.58</v>
       </c>
       <c r="L8" s="84">
         <v>38.12</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="90">
         <v>24.33</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="81">
         <v>11.91</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="85">
         <v>0.74</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="82">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="91">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="86">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="79">
         <v>-10.43</v>
       </c>
       <c r="T8" s="83">
-        <v>39.26</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="9">
@@ -5676,7 +5676,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="100" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,25 +5691,25 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="96">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="101">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="92">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="97">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="93">
         <v>-36.12</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="99">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="94">
         <v>-36.35</v>
       </c>
       <c r="P9" s="98">
@@ -5732,7 +5732,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5747,32 +5747,32 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="102">
         <v>-2.09</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="106">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="104">
+      <c r="K10" s="107">
         <v>-6</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="103">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="110">
         <v>-9.74</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="109">
         <v>-8.97</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="104">
         <v>-10.07</v>
       </c>
       <c r="P10" t="str"/>
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="102">
+      <c r="T10" s="105">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="112" t="str">
+      <c r="D11" s="113" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,41 +5801,41 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="111">
+      <c r="I11" s="117">
         <v>0</v>
       </c>
-      <c r="J11" s="113">
+      <c r="J11" s="114">
         <v>10</v>
       </c>
-      <c r="K11" s="114">
+      <c r="K11" s="115">
         <v>21</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="118">
         <v>33.11</v>
       </c>
       <c r="M11" s="120">
         <v>24.68</v>
       </c>
-      <c r="N11" s="115">
+      <c r="N11" s="121">
         <v>37.11</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="111">
         <v>50.84</v>
       </c>
-      <c r="P11" s="116">
+      <c r="P11" s="122">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="117">
+      <c r="Q11" s="116">
         <v>77.16</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="119">
         <v>59.42</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="112">
         <v>50.05</v>
       </c>
-      <c r="T11" s="118">
-        <v>59.47</v>
+      <c r="T11" s="123">
+        <v>62.68</v>
       </c>
     </row>
     <row r="12">
@@ -5848,7 +5848,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="133" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5863,41 +5863,41 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="127">
+      <c r="I12" s="124">
         <v>8.55</v>
       </c>
-      <c r="J12" s="125">
+      <c r="J12" s="128">
         <v>19.41</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="135">
         <v>11.85</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="125">
         <v>22.99</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="126">
         <v>35.32</v>
       </c>
-      <c r="N12" s="124">
+      <c r="N12" s="134">
         <v>44.48</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="127">
         <v>58.92</v>
       </c>
       <c r="P12" s="129">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="130">
         <v>34.61</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="131">
         <v>45.23</v>
       </c>
-      <c r="S12" s="126">
+      <c r="S12" s="132">
         <v>42.21</v>
       </c>
-      <c r="T12" s="130">
-        <v>43.06</v>
+      <c r="T12" s="136">
+        <v>45.94</v>
       </c>
     </row>
     <row r="13">
@@ -5928,38 +5928,38 @@
       <c r="I13" s="149">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="144">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="138">
+      <c r="K13" s="145">
         <v>-11.5</v>
       </c>
       <c r="L13" s="137">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="141">
+      <c r="M13" s="146">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="142">
+      <c r="N13" s="143">
         <v>-1.22</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="141">
         <v>-4.31</v>
       </c>
-      <c r="P13" s="139">
+      <c r="P13" s="142">
         <v>20.43</v>
       </c>
       <c r="Q13" s="147">
         <v>33.43</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="138">
         <v>31.11</v>
       </c>
-      <c r="S13" s="143">
+      <c r="S13" s="139">
         <v>64.98</v>
       </c>
-      <c r="T13" s="144">
-        <v>8.46</v>
+      <c r="T13" s="148">
+        <v>13.63</v>
       </c>
     </row>
     <row r="14">
@@ -5972,7 +5972,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="156" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -5987,41 +5987,41 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="162">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="154">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="153">
+      <c r="K14" s="150">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="154">
+      <c r="L14" s="159">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="150">
+      <c r="M14" s="160">
         <v>4.78</v>
       </c>
-      <c r="N14" s="151">
+      <c r="N14" s="155">
         <v>1.5</v>
       </c>
-      <c r="O14" s="155">
+      <c r="O14" s="151">
         <v>27.74</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="156">
         <v>41.52</v>
       </c>
       <c r="Q14" s="152">
         <v>39.07</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="157">
         <v>75</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="153">
         <v>60.1</v>
       </c>
       <c r="T14" s="161">
-        <v>15.04</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="15">
@@ -6034,7 +6034,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="164" t="str">
+      <c r="D15" s="175" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,41 +6049,41 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="165">
+      <c r="I15" s="163">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="166">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="172">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="167">
         <v>7.16</v>
       </c>
-      <c r="M15" s="167">
+      <c r="M15" s="168">
         <v>3.81</v>
       </c>
-      <c r="N15" s="168">
+      <c r="N15" s="169">
         <v>30.65</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="170">
         <v>44.75</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="171">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="169">
+      <c r="Q15" s="164">
         <v>78.98</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="165">
         <v>63.75</v>
       </c>
-      <c r="S15" s="166">
+      <c r="S15" s="173">
         <v>56.8</v>
       </c>
-      <c r="T15" s="163">
-        <v>17.66</v>
+      <c r="T15" s="174">
+        <v>23.28</v>
       </c>
     </row>
     <row r="16">
@@ -6096,7 +6096,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="178" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6111,41 +6111,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="179">
+      <c r="I16" s="177">
         <v>-8.1</v>
       </c>
       <c r="J16" s="182">
         <v>-4.7</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="178">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="176">
+      <c r="L16" s="183">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="180">
+      <c r="M16" s="179">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="180">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="177">
+      <c r="O16" s="181">
         <v>8.25</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="186">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="187">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="181">
+      <c r="R16" s="184">
         <v>-5.62</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="188">
         <v>9.38</v>
       </c>
-      <c r="T16" s="185">
-        <v>-24.96</v>
+      <c r="T16" s="176">
+        <v>-21.38</v>
       </c>
     </row>
     <row r="17">
@@ -6158,7 +6158,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="189" t="str">
+      <c r="D17" s="193" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,41 +6173,41 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="190">
+      <c r="I17" s="194">
         <v>3.38</v>
       </c>
-      <c r="J17" s="194">
+      <c r="J17" s="201">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="195">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="191">
+      <c r="L17" s="189">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="192">
         <v>2.69</v>
       </c>
-      <c r="N17" s="192">
+      <c r="N17" s="198">
         <v>17.43</v>
       </c>
-      <c r="O17" s="193">
+      <c r="O17" s="190">
         <v>21.27</v>
       </c>
-      <c r="P17" s="195">
+      <c r="P17" s="196">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="199">
         <v>2.39</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="197">
         <v>18.66</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="191">
         <v>13.27</v>
       </c>
-      <c r="T17" s="197">
-        <v>-18.6</v>
+      <c r="T17" s="200">
+        <v>-14.71</v>
       </c>
     </row>
     <row r="18">
@@ -6220,7 +6220,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="206" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,10 +6235,10 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="206">
+      <c r="I18" s="207">
         <v>0</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="208">
         <v>9.99</v>
       </c>
       <c r="K18" s="202">
@@ -6247,29 +6247,29 @@
       <c r="L18" s="203">
         <v>33.11</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="204">
         <v>19.81</v>
       </c>
-      <c r="N18" s="204">
+      <c r="N18" s="211">
         <v>7.83</v>
       </c>
-      <c r="O18" s="207">
+      <c r="O18" s="209">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="210">
         <v>-12.22</v>
       </c>
       <c r="Q18" s="205">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="208">
+      <c r="R18" s="212">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="213">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="213">
-        <v>-28.01</v>
+      <c r="T18" s="214">
+        <v>-26.8</v>
       </c>
     </row>
     <row r="19">
@@ -6282,7 +6282,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="221" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,41 +6297,41 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="220">
+      <c r="I19" s="222">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="223">
+      <c r="J19" s="215">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="223">
         <v>-7.41</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="226">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="224">
         <v>-9.01</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="216">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="216">
+      <c r="O19" s="227">
         <v>-8.21</v>
       </c>
       <c r="P19" s="217">
         <v>-11.42</v>
       </c>
-      <c r="Q19" s="218">
+      <c r="Q19" s="219">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="219">
+      <c r="R19" s="225">
         <v>-11.35</v>
       </c>
-      <c r="S19" s="221">
+      <c r="S19" s="218">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="215">
-        <v>-22.3</v>
+      <c r="T19" s="220">
+        <v>-21.53</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +6344,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="231" t="str">
+      <c r="D20" s="230" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6359,41 +6359,41 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="238">
         <v>3.51</v>
       </c>
       <c r="J20" s="228">
         <v>10.28</v>
       </c>
-      <c r="K20" s="234">
+      <c r="K20" s="231">
         <v>2.56</v>
       </c>
-      <c r="L20" s="229">
+      <c r="L20" s="232">
         <v>11.62</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="239">
         <v>10.45</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="233">
         <v>8.02</v>
       </c>
-      <c r="O20" s="230">
+      <c r="O20" s="236">
         <v>8.38</v>
       </c>
-      <c r="P20" s="232">
+      <c r="P20" s="237">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="234">
         <v>1.95</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="229">
         <v>28.49</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="240">
         <v>20.94</v>
       </c>
-      <c r="T20" s="233">
-        <v>20.38</v>
+      <c r="T20" s="235">
+        <v>23.98</v>
       </c>
     </row>
     <row r="21">
@@ -6406,7 +6406,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="242" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6421,22 +6421,22 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="243">
+      <c r="I21" s="250">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="243">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="244">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="251">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="244">
+      <c r="M21" s="245">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="241">
+      <c r="N21" s="252">
         <v>-23.72</v>
       </c>
       <c r="O21" s="246">
@@ -6445,17 +6445,17 @@
       <c r="P21" s="247">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="248">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="249">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="242">
+      <c r="S21" s="253">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="245">
-        <v>-22.05</v>
+      <c r="T21" s="241">
+        <v>-20.57</v>
       </c>
     </row>
     <row r="22">
@@ -6483,41 +6483,41 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="261">
+      <c r="I22" s="264">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="258">
+      <c r="J22" s="256">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="254">
+      <c r="K22" s="265">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="266">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="262">
+      <c r="M22" s="257">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="254">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="255">
+      <c r="O22" s="259">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="266">
+      <c r="P22" s="258">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="256">
+      <c r="Q22" s="255">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="259">
+      <c r="R22" s="260">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="257">
+      <c r="S22" s="261">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="260">
-        <v>-32.26</v>
+      <c r="T22" s="262">
+        <v>-31.16</v>
       </c>
     </row>
     <row r="23">
@@ -6530,7 +6530,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="271" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6545,22 +6545,22 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="277">
+      <c r="I23" s="272">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="272">
+      <c r="J23" s="267">
         <v>-9.06</v>
       </c>
       <c r="K23" s="268">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="269">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="277">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="269">
+      <c r="N23" s="278">
         <v>-9.66</v>
       </c>
       <c r="O23" s="273">
@@ -6569,17 +6569,17 @@
       <c r="P23" s="274">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="270">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="267">
+      <c r="R23" s="275">
         <v>-10.32</v>
       </c>
-      <c r="S23" s="270">
+      <c r="S23" s="279">
         <v>-9.91</v>
       </c>
-      <c r="T23" s="271">
-        <v>-3.14</v>
+      <c r="T23" s="276">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="24">
@@ -6641,40 +6641,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="280">
+      <c r="I25" s="287">
         <v>27.27</v>
       </c>
-      <c r="J25" s="286">
+      <c r="J25" s="289">
         <v>45.45</v>
       </c>
-      <c r="K25" s="282">
+      <c r="K25" s="290">
         <v>31.82</v>
       </c>
-      <c r="L25" s="283">
+      <c r="L25" s="285">
         <v>40.91</v>
       </c>
-      <c r="M25" s="287">
+      <c r="M25" s="288">
         <v>40.91</v>
       </c>
-      <c r="N25" s="284">
+      <c r="N25" s="282">
         <v>40.91</v>
       </c>
-      <c r="O25" s="288">
+      <c r="O25" s="291">
         <v>40.91</v>
       </c>
-      <c r="P25" s="289">
+      <c r="P25" s="280">
         <v>47.62</v>
       </c>
-      <c r="Q25" s="291">
+      <c r="Q25" s="286">
         <v>40</v>
       </c>
-      <c r="R25" s="285">
+      <c r="R25" s="283">
         <v>40</v>
       </c>
       <c r="S25" s="281">
         <v>45</v>
       </c>
-      <c r="T25" s="290">
+      <c r="T25" s="284">
         <v>36.36</v>
       </c>
     </row>
@@ -6689,41 +6689,41 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="299">
+      <c r="I26" s="295">
         <v>-1.94</v>
       </c>
-      <c r="J26" s="296">
+      <c r="J26" s="301">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="297">
+      <c r="K26" s="296">
         <v>-1.81</v>
       </c>
-      <c r="L26" s="300">
+      <c r="L26" s="302">
         <v>-0.48</v>
       </c>
-      <c r="M26" s="293">
+      <c r="M26" s="294">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="301">
+      <c r="N26" s="303">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="302">
+      <c r="O26" s="292">
         <v>1.67</v>
       </c>
-      <c r="P26" s="294">
+      <c r="P26" s="298">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="295">
+      <c r="Q26" s="297">
         <v>4.66</v>
       </c>
-      <c r="R26" s="292">
+      <c r="R26" s="293">
         <v>7.06</v>
       </c>
-      <c r="S26" s="303">
+      <c r="S26" s="299">
         <v>7.81</v>
       </c>
-      <c r="T26" s="298">
-        <v>-5.15</v>
+      <c r="T26" s="300">
+        <v>-3.64</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -57,6 +57,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -69,24 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -99,13 +117,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,1591 +213,1549 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8EFDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1B7632"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
+        <fgColor rgb="FF3BAF55"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1719,7 +1767,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1731,55 +1785,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1791,7 +1815,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1803,55 +1827,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF2EA94A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5242,7 +5242,7 @@
       <c r="C2" t="str">
         <v>605398</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="11" t="str">
         <v>净买: 309.39万</v>
       </c>
       <c r="E2">
@@ -5257,41 +5257,41 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="5">
         <v>10.01</v>
       </c>
       <c r="K2" s="6">
         <v>17.19</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="13">
         <v>5.47</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="7">
         <v>-4.76</v>
       </c>
       <c r="N2" s="1">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="8">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="9">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="10">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="12">
         <v>-16.59</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="9">
-        <v>-38.87</v>
+      <c r="T2" s="3">
+        <v>-40.03</v>
       </c>
     </row>
     <row r="3">
@@ -5304,7 +5304,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="20" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5319,41 +5319,41 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="17">
         <v>7.24</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="26">
         <v>4.08</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="18">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="21">
         <v>0.96</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="22">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="14">
         <v>-11</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="15">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="16">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="23">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="25">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="24">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="23">
-        <v>-17.42</v>
+      <c r="T3" s="19">
+        <v>-18.19</v>
       </c>
     </row>
     <row r="4">
@@ -5366,7 +5366,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,25 +5381,25 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="28">
         <v>0</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="34">
         <v>0.15</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="35">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="31">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="37">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="32">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="38">
         <v>-21.93</v>
       </c>
       <c r="P4" s="29">
@@ -5408,14 +5408,14 @@
       <c r="Q4" s="30">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="33">
         <v>-22.78</v>
       </c>
       <c r="S4" s="39">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="31">
-        <v>-22.93</v>
+      <c r="T4" s="27">
+        <v>-23.08</v>
       </c>
     </row>
     <row r="5">
@@ -5428,7 +5428,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5443,41 +5443,41 @@
       <c r="H5">
         <v>-2.91</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="48">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="44">
         <v>1.94</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="40">
         <v>4</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="45">
         <v>4.69</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="46">
         <v>11.75</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="52">
         <v>4.44</v>
       </c>
       <c r="O5" s="47">
         <v>6.5</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="41">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="42">
         <v>2</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="49">
         <v>12.19</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="50">
         <v>20.06</v>
       </c>
-      <c r="T5" s="42">
-        <v>33.31</v>
+      <c r="T5" s="43">
+        <v>30.13</v>
       </c>
     </row>
     <row r="6">
@@ -5490,7 +5490,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="54" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5505,41 +5505,41 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="60">
         <v>9.1</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="53">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="57">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="54">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="63">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="64">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="55">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="56">
         <v>-18.71</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="61">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="58">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="62">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="64">
-        <v>-37.56</v>
+      <c r="T6" s="59">
+        <v>-37.3</v>
       </c>
     </row>
     <row r="7">
@@ -5552,7 +5552,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,41 +5567,41 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="69">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="74">
         <v>0.95</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="66">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="67">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="71">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="72">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="75">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="76">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="70">
         <v>-8.59</v>
       </c>
       <c r="R7" s="77">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="78">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="74">
-        <v>-29.44</v>
+      <c r="T7" s="73">
+        <v>-29.15</v>
       </c>
     </row>
     <row r="8">
@@ -5614,7 +5614,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="81" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,41 +5629,41 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="82">
         <v>3.82</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="88">
         <v>14.19</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="83">
         <v>25.58</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="86">
         <v>38.12</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="87">
         <v>24.33</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="91">
         <v>11.91</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="84">
         <v>0.74</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="79">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="89">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="85">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="80">
         <v>-10.43</v>
       </c>
-      <c r="T8" s="83">
-        <v>29.69</v>
+      <c r="T8" s="90">
+        <v>28.09</v>
       </c>
     </row>
     <row r="9">
@@ -5676,7 +5676,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="101" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,34 +5691,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="94">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="97">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="95">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="96">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="98">
         <v>-36.12</v>
       </c>
       <c r="N9" s="99">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="92">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="100">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="95">
+      <c r="T9" s="93">
         <v>-37.12</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="106" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5747,32 +5747,32 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="102">
+      <c r="I10" s="103">
         <v>-2.09</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="109">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="110">
         <v>-6</v>
       </c>
-      <c r="L10" s="103">
+      <c r="L10" s="104">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="102">
         <v>-9.74</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="105">
         <v>-8.97</v>
       </c>
-      <c r="O10" s="104">
+      <c r="O10" s="107">
         <v>-10.07</v>
       </c>
       <c r="P10" t="str"/>
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="105">
+      <c r="T10" s="108">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="113" t="str">
+      <c r="D11" s="119" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,41 +5801,41 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="117">
+      <c r="I11" s="120">
         <v>0</v>
       </c>
       <c r="J11" s="114">
         <v>10</v>
       </c>
-      <c r="K11" s="115">
+      <c r="K11" s="123">
         <v>21</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="115">
         <v>33.11</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="116">
         <v>24.68</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="111">
         <v>37.11</v>
       </c>
-      <c r="O11" s="111">
+      <c r="O11" s="121">
         <v>50.84</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="112">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="116">
+      <c r="Q11" s="113">
         <v>77.16</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="117">
         <v>59.42</v>
       </c>
-      <c r="S11" s="112">
+      <c r="S11" s="118">
         <v>50.05</v>
       </c>
-      <c r="T11" s="123">
-        <v>62.68</v>
+      <c r="T11" s="122">
+        <v>62.05</v>
       </c>
     </row>
     <row r="12">
@@ -5848,7 +5848,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="136" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5866,38 +5866,38 @@
       <c r="I12" s="124">
         <v>8.55</v>
       </c>
-      <c r="J12" s="128">
+      <c r="J12" s="125">
         <v>19.41</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="126">
         <v>11.85</v>
       </c>
-      <c r="L12" s="125">
+      <c r="L12" s="128">
         <v>22.99</v>
       </c>
-      <c r="M12" s="126">
+      <c r="M12" s="130">
         <v>35.32</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="131">
         <v>44.48</v>
       </c>
-      <c r="O12" s="127">
+      <c r="O12" s="134">
         <v>58.92</v>
       </c>
-      <c r="P12" s="129">
+      <c r="P12" s="127">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="130">
+      <c r="Q12" s="129">
         <v>34.61</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="135">
         <v>45.23</v>
       </c>
       <c r="S12" s="132">
         <v>42.21</v>
       </c>
-      <c r="T12" s="136">
-        <v>45.94</v>
+      <c r="T12" s="133">
+        <v>45.37</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +5910,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="140" t="str">
+      <c r="D13" s="143" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5925,41 +5925,41 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="146">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="144">
+      <c r="J13" s="137">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="140">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="137">
+      <c r="L13" s="147">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="144">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="143">
+      <c r="N13" s="145">
         <v>-1.22</v>
       </c>
-      <c r="O13" s="141">
+      <c r="O13" s="138">
         <v>-4.31</v>
       </c>
-      <c r="P13" s="142">
+      <c r="P13" s="141">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="139">
         <v>33.43</v>
       </c>
-      <c r="R13" s="138">
+      <c r="R13" s="142">
         <v>31.11</v>
       </c>
-      <c r="S13" s="139">
+      <c r="S13" s="148">
         <v>64.98</v>
       </c>
-      <c r="T13" s="148">
-        <v>13.63</v>
+      <c r="T13" s="149">
+        <v>9.13</v>
       </c>
     </row>
     <row r="14">
@@ -5972,7 +5972,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="154" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -5987,41 +5987,41 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="155">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="154">
+      <c r="J14" s="162">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="150">
+      <c r="K14" s="160">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="156">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="150">
         <v>4.78</v>
       </c>
-      <c r="N14" s="155">
+      <c r="N14" s="152">
         <v>1.5</v>
       </c>
-      <c r="O14" s="151">
+      <c r="O14" s="161">
         <v>27.74</v>
       </c>
-      <c r="P14" s="156">
+      <c r="P14" s="157">
         <v>41.52</v>
       </c>
-      <c r="Q14" s="152">
+      <c r="Q14" s="158">
         <v>39.07</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="153">
         <v>75</v>
       </c>
-      <c r="S14" s="153">
+      <c r="S14" s="159">
         <v>60.1</v>
       </c>
-      <c r="T14" s="161">
-        <v>20.53</v>
+      <c r="T14" s="151">
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -6034,7 +6034,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="163" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,41 +6049,41 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="163">
+      <c r="I15" s="171">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="166">
+      <c r="J15" s="170">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="164">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="167">
+      <c r="L15" s="173">
         <v>7.16</v>
       </c>
-      <c r="M15" s="168">
+      <c r="M15" s="174">
         <v>3.81</v>
       </c>
-      <c r="N15" s="169">
+      <c r="N15" s="175">
         <v>30.65</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="165">
         <v>44.75</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="166">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="164">
+      <c r="Q15" s="172">
         <v>78.98</v>
       </c>
-      <c r="R15" s="165">
+      <c r="R15" s="167">
         <v>63.75</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="168">
         <v>56.8</v>
       </c>
-      <c r="T15" s="174">
-        <v>23.28</v>
+      <c r="T15" s="169">
+        <v>18.39</v>
       </c>
     </row>
     <row r="16">
@@ -6096,7 +6096,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="187" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6111,41 +6111,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="184">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="182">
+      <c r="J16" s="188">
         <v>-4.7</v>
       </c>
-      <c r="K16" s="178">
+      <c r="K16" s="180">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="181">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="179">
+      <c r="M16" s="176">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="180">
+      <c r="N16" s="182">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="181">
+      <c r="O16" s="177">
         <v>8.25</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="185">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="179">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="184">
+      <c r="R16" s="183">
         <v>-5.62</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="186">
         <v>9.38</v>
       </c>
-      <c r="T16" s="176">
-        <v>-21.38</v>
+      <c r="T16" s="178">
+        <v>-24.5</v>
       </c>
     </row>
     <row r="17">
@@ -6158,7 +6158,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="193" t="str">
+      <c r="D17" s="189" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,19 +6173,19 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="194">
+      <c r="I17" s="195">
         <v>3.38</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="192">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="195">
+      <c r="K17" s="196">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="189">
+      <c r="L17" s="197">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="192">
+      <c r="M17" s="193">
         <v>2.69</v>
       </c>
       <c r="N17" s="198">
@@ -6194,20 +6194,20 @@
       <c r="O17" s="190">
         <v>21.27</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="199">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="194">
         <v>2.39</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="200">
         <v>18.66</v>
       </c>
-      <c r="S17" s="191">
+      <c r="S17" s="201">
         <v>13.27</v>
       </c>
-      <c r="T17" s="200">
-        <v>-14.71</v>
+      <c r="T17" s="191">
+        <v>-18.09</v>
       </c>
     </row>
     <row r="18">
@@ -6220,7 +6220,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="206" t="str">
+      <c r="D18" s="208" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,41 +6235,41 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="207">
+      <c r="I18" s="209">
         <v>0</v>
       </c>
-      <c r="J18" s="208">
+      <c r="J18" s="203">
         <v>9.99</v>
       </c>
-      <c r="K18" s="202">
+      <c r="K18" s="211">
         <v>20.99</v>
       </c>
-      <c r="L18" s="203">
+      <c r="L18" s="212">
         <v>33.11</v>
       </c>
-      <c r="M18" s="204">
+      <c r="M18" s="213">
         <v>19.81</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="214">
         <v>7.83</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="206">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="207">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="205">
+      <c r="Q18" s="202">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="204">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="205">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="214">
-        <v>-26.8</v>
+      <c r="T18" s="210">
+        <v>-27.24</v>
       </c>
     </row>
     <row r="19">
@@ -6282,7 +6282,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="221" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,41 +6297,41 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="227">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="218">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="219">
         <v>-7.41</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="215">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="223">
         <v>-9.01</v>
       </c>
       <c r="N19" s="216">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="220">
         <v>-8.21</v>
       </c>
-      <c r="P19" s="217">
+      <c r="P19" s="221">
         <v>-11.42</v>
       </c>
-      <c r="Q19" s="219">
+      <c r="Q19" s="217">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="224">
         <v>-11.35</v>
       </c>
-      <c r="S19" s="218">
+      <c r="S19" s="222">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="220">
-        <v>-21.53</v>
+      <c r="T19" s="225">
+        <v>-24.6</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +6344,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="230" t="str">
+      <c r="D20" s="235" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6359,41 +6359,41 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="228">
         <v>3.51</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="229">
         <v>10.28</v>
       </c>
-      <c r="K20" s="231">
+      <c r="K20" s="236">
         <v>2.56</v>
       </c>
-      <c r="L20" s="232">
+      <c r="L20" s="230">
         <v>11.62</v>
       </c>
       <c r="M20" s="239">
         <v>10.45</v>
       </c>
-      <c r="N20" s="233">
+      <c r="N20" s="237">
         <v>8.02</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="233">
         <v>8.38</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="234">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="234">
+      <c r="Q20" s="231">
         <v>1.95</v>
       </c>
-      <c r="R20" s="229">
+      <c r="R20" s="232">
         <v>28.49</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="238">
         <v>20.94</v>
       </c>
-      <c r="T20" s="235">
-        <v>23.98</v>
+      <c r="T20" s="240">
+        <v>20.89</v>
       </c>
     </row>
     <row r="21">
@@ -6406,7 +6406,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="242" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6421,41 +6421,41 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="245">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="243">
+      <c r="J21" s="253">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="244">
+      <c r="K21" s="246">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="247">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="245">
+      <c r="M21" s="242">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="248">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="246">
+      <c r="O21" s="251">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="247">
+      <c r="P21" s="241">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="249">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="250">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="243">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="241">
-        <v>-20.57</v>
+      <c r="T21" s="244">
+        <v>-20.05</v>
       </c>
     </row>
     <row r="22">
@@ -6468,7 +6468,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="256" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6483,41 +6483,41 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="257">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="256">
+      <c r="J22" s="263">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="258">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="259">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="257">
+      <c r="M22" s="266">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="254">
+      <c r="N22" s="260">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="259">
+      <c r="O22" s="261">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="258">
+      <c r="P22" s="264">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="255">
+      <c r="Q22" s="265">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="260">
+      <c r="R22" s="254">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="262">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="262">
-        <v>-31.16</v>
+      <c r="T22" s="255">
+        <v>-30.54</v>
       </c>
     </row>
     <row r="23">
@@ -6530,7 +6530,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="271" t="str">
+      <c r="D23" s="274" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6545,10 +6545,10 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="272">
+      <c r="I23" s="275">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="267">
+      <c r="J23" s="276">
         <v>-9.06</v>
       </c>
       <c r="K23" s="268">
@@ -6557,29 +6557,29 @@
       <c r="L23" s="269">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="277">
+      <c r="M23" s="270">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="271">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="273">
+      <c r="O23" s="272">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="277">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="270">
+      <c r="Q23" s="278">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="273">
         <v>-10.32</v>
       </c>
       <c r="S23" s="279">
         <v>-9.91</v>
       </c>
-      <c r="T23" s="276">
-        <v>-3.48</v>
+      <c r="T23" s="267">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="24">
@@ -6641,40 +6641,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="287">
+      <c r="I25" s="289">
         <v>27.27</v>
       </c>
-      <c r="J25" s="289">
+      <c r="J25" s="290">
         <v>45.45</v>
       </c>
-      <c r="K25" s="290">
+      <c r="K25" s="286">
         <v>31.82</v>
       </c>
-      <c r="L25" s="285">
+      <c r="L25" s="291">
         <v>40.91</v>
       </c>
-      <c r="M25" s="288">
+      <c r="M25" s="280">
         <v>40.91</v>
       </c>
-      <c r="N25" s="282">
+      <c r="N25" s="281">
         <v>40.91</v>
       </c>
-      <c r="O25" s="291">
+      <c r="O25" s="287">
         <v>40.91</v>
       </c>
-      <c r="P25" s="280">
+      <c r="P25" s="288">
         <v>47.62</v>
       </c>
-      <c r="Q25" s="286">
+      <c r="Q25" s="285">
         <v>40</v>
       </c>
-      <c r="R25" s="283">
+      <c r="R25" s="282">
         <v>40</v>
       </c>
-      <c r="S25" s="281">
+      <c r="S25" s="284">
         <v>45</v>
       </c>
-      <c r="T25" s="284">
+      <c r="T25" s="283">
         <v>36.36</v>
       </c>
     </row>
@@ -6689,41 +6689,41 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="295">
+      <c r="I26" s="302">
         <v>-1.94</v>
       </c>
-      <c r="J26" s="301">
+      <c r="J26" s="294">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="296">
+      <c r="K26" s="295">
         <v>-1.81</v>
       </c>
-      <c r="L26" s="302">
+      <c r="L26" s="292">
         <v>-0.48</v>
       </c>
-      <c r="M26" s="294">
+      <c r="M26" s="298">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="303">
+      <c r="N26" s="293">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="292">
+      <c r="O26" s="296">
         <v>1.67</v>
       </c>
-      <c r="P26" s="298">
+      <c r="P26" s="297">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="297">
+      <c r="Q26" s="303">
         <v>4.66</v>
       </c>
-      <c r="R26" s="293">
+      <c r="R26" s="299">
         <v>7.06</v>
       </c>
-      <c r="S26" s="299">
+      <c r="S26" s="300">
         <v>7.81</v>
       </c>
-      <c r="T26" s="300">
-        <v>-3.64</v>
+      <c r="T26" s="301">
+        <v>-5.05</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -57,25 +57,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,19 +405,919 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,19 +1329,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,7 +1545,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,121 +1755,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,13 +1797,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,1543 +1839,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8EFDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -5242,7 +5242,7 @@
       <c r="C2" t="str">
         <v>605398</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 309.39万</v>
       </c>
       <c r="E2">
@@ -5257,7 +5257,7 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
       <c r="J2" s="5">
@@ -5266,22 +5266,22 @@
       <c r="K2" s="6">
         <v>17.19</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="7">
         <v>5.47</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="13">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="8">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="1">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="10">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="11">
         <v>-11.9</v>
       </c>
       <c r="R2" s="12">
@@ -5291,7 +5291,7 @@
         <v>-15.48</v>
       </c>
       <c r="T2" s="3">
-        <v>-40.03</v>
+        <v>-39.67</v>
       </c>
     </row>
     <row r="3">
@@ -5304,7 +5304,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5319,41 +5319,41 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="26">
         <v>7.24</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="14">
         <v>4.08</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="19">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="20">
         <v>0.96</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="15">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="21">
         <v>-11</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="16">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="23">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="22">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="24">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="25">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="19">
-        <v>-18.19</v>
+      <c r="T3" s="17">
+        <v>-18.1</v>
       </c>
     </row>
     <row r="4">
@@ -5366,7 +5366,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,41 +5381,41 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="29">
         <v>0</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="28">
         <v>0.15</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="30">
         <v>-9.89</v>
       </c>
       <c r="L4" s="31">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="35">
         <v>-20.71</v>
       </c>
       <c r="N4" s="32">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="39">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="36">
         <v>-23.39</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="27">
         <v>-23.47</v>
       </c>
       <c r="R4" s="33">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="37">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="27">
-        <v>-23.08</v>
+      <c r="T4" s="38">
+        <v>-20.78</v>
       </c>
     </row>
     <row r="5">
@@ -5428,7 +5428,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="42" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5446,38 +5446,38 @@
       <c r="I5" s="48">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="49">
         <v>1.94</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="51">
         <v>4</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="52">
         <v>4.69</v>
       </c>
       <c r="M5" s="46">
         <v>11.75</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="43">
         <v>4.44</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="50">
         <v>6.5</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="40">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="44">
         <v>2</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="45">
         <v>12.19</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="41">
         <v>20.06</v>
       </c>
-      <c r="T5" s="43">
-        <v>30.13</v>
+      <c r="T5" s="47">
+        <v>26.31</v>
       </c>
     </row>
     <row r="6">
@@ -5490,7 +5490,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5505,41 +5505,41 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="62">
         <v>9.1</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="55">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="56">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="65">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="57">
         <v>-13.91</v>
       </c>
       <c r="N6" s="64">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="53">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="63">
         <v>-18.71</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="58">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="59">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="60">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="59">
-        <v>-37.3</v>
+      <c r="T6" s="54">
+        <v>-38.6</v>
       </c>
     </row>
     <row r="7">
@@ -5552,7 +5552,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,41 +5567,41 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="66">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="69">
         <v>0.95</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="74">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="70">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="75">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="76">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="67">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="71">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="72">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="73">
         <v>-7.34</v>
       </c>
       <c r="S7" s="78">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="73">
-        <v>-29.15</v>
+      <c r="T7" s="68">
+        <v>-30.62</v>
       </c>
     </row>
     <row r="8">
@@ -5614,7 +5614,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="85" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,41 +5629,41 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="86">
         <v>3.82</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="87">
         <v>14.19</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="88">
         <v>25.58</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="89">
         <v>38.12</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="83">
         <v>24.33</v>
       </c>
       <c r="N8" s="91">
         <v>11.91</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="80">
         <v>0.74</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="81">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="79">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="84">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="82">
         <v>-10.43</v>
       </c>
       <c r="T8" s="90">
-        <v>28.09</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="9">
@@ -5676,7 +5676,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="94" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,34 +5691,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="95">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="92">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="96">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="98">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="93">
         <v>-36.12</v>
       </c>
       <c r="N9" s="99">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="97">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="101">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="93">
+      <c r="T9" s="100">
         <v>-37.12</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="103" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5747,22 +5747,22 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="104">
         <v>-2.09</v>
       </c>
       <c r="J10" s="109">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="108">
         <v>-6</v>
       </c>
-      <c r="L10" s="104">
+      <c r="L10" s="110">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="105">
         <v>-9.74</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="106">
         <v>-8.97</v>
       </c>
       <c r="O10" s="107">
@@ -5772,7 +5772,7 @@
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="108">
+      <c r="T10" s="102">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="119" t="str">
+      <c r="D11" s="120" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,41 +5801,41 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="117">
         <v>0</v>
       </c>
-      <c r="J11" s="114">
+      <c r="J11" s="113">
         <v>10</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="121">
         <v>21</v>
       </c>
-      <c r="L11" s="115">
+      <c r="L11" s="122">
         <v>33.11</v>
       </c>
-      <c r="M11" s="116">
+      <c r="M11" s="114">
         <v>24.68</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="123">
         <v>37.11</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="115">
         <v>50.84</v>
       </c>
-      <c r="P11" s="112">
+      <c r="P11" s="111">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="113">
+      <c r="Q11" s="118">
         <v>77.16</v>
       </c>
-      <c r="R11" s="117">
+      <c r="R11" s="116">
         <v>59.42</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="112">
         <v>50.05</v>
       </c>
-      <c r="T11" s="122">
-        <v>62.05</v>
+      <c r="T11" s="119">
+        <v>54.84</v>
       </c>
     </row>
     <row r="12">
@@ -5848,7 +5848,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="124" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5863,41 +5863,41 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="124">
+      <c r="I12" s="135">
         <v>8.55</v>
       </c>
-      <c r="J12" s="125">
+      <c r="J12" s="129">
         <v>19.41</v>
       </c>
-      <c r="K12" s="126">
+      <c r="K12" s="131">
         <v>11.85</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="125">
         <v>22.99</v>
       </c>
-      <c r="M12" s="130">
+      <c r="M12" s="132">
         <v>35.32</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="133">
         <v>44.48</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="126">
         <v>58.92</v>
       </c>
       <c r="P12" s="127">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="129">
+      <c r="Q12" s="136">
         <v>34.61</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="134">
         <v>45.23</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="128">
         <v>42.21</v>
       </c>
-      <c r="T12" s="133">
-        <v>45.37</v>
+      <c r="T12" s="130">
+        <v>38.9</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +5910,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="143" t="str">
+      <c r="D13" s="142" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5925,41 +5925,41 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="137">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="137">
+      <c r="J13" s="146">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="140">
+      <c r="K13" s="138">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="139">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="140">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="147">
         <v>-1.22</v>
       </c>
-      <c r="O13" s="138">
+      <c r="O13" s="143">
         <v>-4.31</v>
       </c>
       <c r="P13" s="141">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="139">
+      <c r="Q13" s="144">
         <v>33.43</v>
       </c>
-      <c r="R13" s="142">
+      <c r="R13" s="145">
         <v>31.11</v>
       </c>
       <c r="S13" s="148">
         <v>64.98</v>
       </c>
       <c r="T13" s="149">
-        <v>9.13</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="14">
@@ -5972,7 +5972,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="154" t="str">
+      <c r="D14" s="155" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -5987,41 +5987,41 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="155">
+      <c r="I14" s="156">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="150">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="157">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="156">
+      <c r="L14" s="158">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="150">
+      <c r="M14" s="151">
         <v>4.78</v>
       </c>
       <c r="N14" s="152">
         <v>1.5</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="159">
         <v>27.74</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="160">
         <v>41.52</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="153">
         <v>39.07</v>
       </c>
-      <c r="R14" s="153">
+      <c r="R14" s="161">
         <v>75</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="154">
         <v>60.1</v>
       </c>
-      <c r="T14" s="151">
-        <v>15.75</v>
+      <c r="T14" s="162">
+        <v>8.75</v>
       </c>
     </row>
     <row r="15">
@@ -6034,7 +6034,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="163" t="str">
+      <c r="D15" s="171" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,41 +6049,41 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="172">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="165">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="164">
+      <c r="K15" s="166">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="167">
         <v>7.16</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="173">
         <v>3.81</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="163">
         <v>30.65</v>
       </c>
-      <c r="O15" s="165">
+      <c r="O15" s="168">
         <v>44.75</v>
       </c>
-      <c r="P15" s="166">
+      <c r="P15" s="174">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="169">
         <v>78.98</v>
       </c>
-      <c r="R15" s="167">
+      <c r="R15" s="175">
         <v>63.75</v>
       </c>
-      <c r="S15" s="168">
+      <c r="S15" s="164">
         <v>56.8</v>
       </c>
-      <c r="T15" s="169">
-        <v>18.39</v>
+      <c r="T15" s="170">
+        <v>11.23</v>
       </c>
     </row>
     <row r="16">
@@ -6096,7 +6096,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="187" t="str">
+      <c r="D16" s="177" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6111,41 +6111,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="188">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="178">
         <v>-4.7</v>
       </c>
       <c r="K16" s="180">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="181">
+      <c r="L16" s="183">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="176">
+      <c r="M16" s="184">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="182">
+      <c r="N16" s="181">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="177">
+      <c r="O16" s="176">
         <v>8.25</v>
       </c>
       <c r="P16" s="185">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="179">
+      <c r="Q16" s="182">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="179">
         <v>-5.62</v>
       </c>
       <c r="S16" s="186">
         <v>9.38</v>
       </c>
-      <c r="T16" s="178">
-        <v>-24.5</v>
+      <c r="T16" s="187">
+        <v>-29.07</v>
       </c>
     </row>
     <row r="17">
@@ -6158,7 +6158,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="189" t="str">
+      <c r="D17" s="190" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,41 +6173,41 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="195">
+      <c r="I17" s="201">
         <v>3.38</v>
       </c>
-      <c r="J17" s="192">
+      <c r="J17" s="193">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="197">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="189">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="193">
+      <c r="M17" s="198">
         <v>2.69</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="194">
         <v>17.43</v>
       </c>
-      <c r="O17" s="190">
+      <c r="O17" s="191">
         <v>21.27</v>
       </c>
       <c r="P17" s="199">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="194">
+      <c r="Q17" s="195">
         <v>2.39</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="192">
         <v>18.66</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="196">
         <v>13.27</v>
       </c>
-      <c r="T17" s="191">
-        <v>-18.09</v>
+      <c r="T17" s="200">
+        <v>-23.05</v>
       </c>
     </row>
     <row r="18">
@@ -6220,7 +6220,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="208" t="str">
+      <c r="D18" s="214" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,41 +6235,41 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="205">
         <v>0</v>
       </c>
-      <c r="J18" s="203">
+      <c r="J18" s="209">
         <v>9.99</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="206">
         <v>20.99</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="213">
         <v>33.11</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="202">
         <v>19.81</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="207">
         <v>7.83</v>
       </c>
-      <c r="O18" s="206">
+      <c r="O18" s="208">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="207">
+      <c r="P18" s="210">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="202">
+      <c r="Q18" s="211">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="204">
+      <c r="R18" s="212">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="205">
+      <c r="S18" s="203">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="210">
-        <v>-27.24</v>
+      <c r="T18" s="204">
+        <v>-23.59</v>
       </c>
     </row>
     <row r="19">
@@ -6282,7 +6282,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="219" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,19 +6297,19 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="226">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="218">
+      <c r="J19" s="224">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="219">
+      <c r="K19" s="227">
         <v>-7.41</v>
       </c>
       <c r="L19" s="215">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="225">
         <v>-9.01</v>
       </c>
       <c r="N19" s="216">
@@ -6324,14 +6324,14 @@
       <c r="Q19" s="217">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="224">
+      <c r="R19" s="218">
         <v>-11.35</v>
       </c>
       <c r="S19" s="222">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="225">
-        <v>-24.6</v>
+      <c r="T19" s="223">
+        <v>-26.5</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +6344,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="231" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6365,35 +6365,35 @@
       <c r="J20" s="229">
         <v>10.28</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="232">
         <v>2.56</v>
       </c>
-      <c r="L20" s="230">
+      <c r="L20" s="235">
         <v>11.62</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="233">
         <v>10.45</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="230">
         <v>8.02</v>
       </c>
-      <c r="O20" s="233">
+      <c r="O20" s="236">
         <v>8.38</v>
       </c>
       <c r="P20" s="234">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="231">
+      <c r="Q20" s="237">
         <v>1.95</v>
       </c>
-      <c r="R20" s="232">
+      <c r="R20" s="238">
         <v>28.49</v>
       </c>
-      <c r="S20" s="238">
+      <c r="S20" s="239">
         <v>20.94</v>
       </c>
       <c r="T20" s="240">
-        <v>20.89</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="21">
@@ -6406,7 +6406,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6424,38 +6424,38 @@
       <c r="I21" s="245">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="243">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="246">
+      <c r="K21" s="247">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="247">
+      <c r="L21" s="244">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="242">
+      <c r="M21" s="252">
         <v>-21.05</v>
       </c>
       <c r="N21" s="248">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="253">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="241">
+      <c r="P21" s="246">
         <v>-24.31</v>
       </c>
       <c r="Q21" s="249">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="241">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="243">
+      <c r="S21" s="242">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="244">
-        <v>-20.05</v>
+      <c r="T21" s="250">
+        <v>-19.76</v>
       </c>
     </row>
     <row r="22">
@@ -6468,7 +6468,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="256" t="str">
+      <c r="D22" s="265" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6483,41 +6483,41 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="257">
+      <c r="I22" s="266">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="256">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="258">
+      <c r="K22" s="262">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="259">
+      <c r="L22" s="258">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="266">
+      <c r="M22" s="263">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="260">
+      <c r="N22" s="254">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="255">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="264">
+      <c r="P22" s="259">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="260">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="254">
+      <c r="R22" s="261">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="257">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="255">
-        <v>-30.54</v>
+      <c r="T22" s="264">
+        <v>-33.51</v>
       </c>
     </row>
     <row r="23">
@@ -6530,7 +6530,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="268" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6545,41 +6545,41 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="276">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="269">
         <v>-9.06</v>
       </c>
-      <c r="K23" s="268">
+      <c r="K23" s="270">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="269">
+      <c r="L23" s="271">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="270">
+      <c r="M23" s="272">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="271">
+      <c r="N23" s="277">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="272">
+      <c r="O23" s="278">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="273">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="274">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="273">
+      <c r="R23" s="279">
         <v>-10.32</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="275">
         <v>-9.91</v>
       </c>
       <c r="T23" s="267">
-        <v>-0.89</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="24">
@@ -6641,40 +6641,40 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="289">
+      <c r="I25" s="288">
         <v>27.27</v>
       </c>
-      <c r="J25" s="290">
+      <c r="J25" s="289">
         <v>45.45</v>
       </c>
       <c r="K25" s="286">
         <v>31.82</v>
       </c>
-      <c r="L25" s="291">
+      <c r="L25" s="287">
         <v>40.91</v>
       </c>
-      <c r="M25" s="280">
+      <c r="M25" s="290">
         <v>40.91</v>
       </c>
       <c r="N25" s="281">
         <v>40.91</v>
       </c>
-      <c r="O25" s="287">
+      <c r="O25" s="282">
         <v>40.91</v>
       </c>
-      <c r="P25" s="288">
+      <c r="P25" s="291">
         <v>47.62</v>
       </c>
-      <c r="Q25" s="285">
+      <c r="Q25" s="284">
         <v>40</v>
       </c>
-      <c r="R25" s="282">
+      <c r="R25" s="285">
         <v>40</v>
       </c>
-      <c r="S25" s="284">
+      <c r="S25" s="283">
         <v>45</v>
       </c>
-      <c r="T25" s="283">
+      <c r="T25" s="280">
         <v>36.36</v>
       </c>
     </row>
@@ -6689,41 +6689,41 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="302">
+      <c r="I26" s="294">
         <v>-1.94</v>
       </c>
-      <c r="J26" s="294">
+      <c r="J26" s="295">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="295">
+      <c r="K26" s="303">
         <v>-1.81</v>
       </c>
-      <c r="L26" s="292">
+      <c r="L26" s="296">
         <v>-0.48</v>
       </c>
       <c r="M26" s="298">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="293">
+      <c r="N26" s="299">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="296">
+      <c r="O26" s="297">
         <v>1.67</v>
       </c>
-      <c r="P26" s="297">
+      <c r="P26" s="292">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="303">
+      <c r="Q26" s="300">
         <v>4.66</v>
       </c>
-      <c r="R26" s="299">
+      <c r="R26" s="293">
         <v>7.06</v>
       </c>
-      <c r="S26" s="300">
+      <c r="S26" s="301">
         <v>7.81</v>
       </c>
-      <c r="T26" s="301">
-        <v>-5.05</v>
+      <c r="T26" s="302">
+        <v>-7.47</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="305">
+  <fills count="307">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -63,6 +111,168 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -75,13 +285,463 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,31 +753,1003 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,151 +1761,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,1519 +1815,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FF69C17D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1807,56 +1867,22 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="304">
+  <borders count="306">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -3989,7 +4015,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="306">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4898,6 +4924,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="303" fillId="304" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="304" fillId="305" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="305" fillId="306" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5242,7 +5274,7 @@
       <c r="C2" t="str">
         <v>605398</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 309.39万</v>
       </c>
       <c r="E2">
@@ -5257,41 +5289,41 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="13">
         <v>0</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="1">
         <v>10.01</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="7">
         <v>17.19</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="8">
         <v>5.47</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="2">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="3">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="9">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="5">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="6">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="10">
         <v>-16.59</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="11">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="3">
-        <v>-39.67</v>
+      <c r="T2" s="4">
+        <v>-39.45</v>
       </c>
     </row>
     <row r="3">
@@ -5304,7 +5336,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5322,38 +5354,38 @@
       <c r="I3" s="26">
         <v>7.24</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="23">
         <v>4.08</v>
       </c>
       <c r="K3" s="19">
         <v>-1.56</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="24">
         <v>0.96</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="14">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="20">
         <v>-11</v>
       </c>
       <c r="O3" s="16">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="21">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="17">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="18">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="22">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="17">
-        <v>-18.1</v>
+      <c r="T3" s="25">
+        <v>-9.9</v>
       </c>
     </row>
     <row r="4">
@@ -5366,7 +5398,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5381,40 +5413,40 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="32">
         <v>0</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="33">
         <v>0.15</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="28">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="35">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="36">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="38">
         <v>-21.78</v>
       </c>
       <c r="O4" s="39">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="29">
         <v>-23.39</v>
       </c>
       <c r="Q4" s="27">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="37">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="30">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="34">
         <v>-20.78</v>
       </c>
     </row>
@@ -5428,7 +5460,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="47" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5446,38 +5478,38 @@
       <c r="I5" s="48">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="42">
         <v>1.94</v>
       </c>
       <c r="K5" s="51">
         <v>4</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="43">
         <v>4.69</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="45">
         <v>11.75</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="49">
         <v>4.44</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="44">
         <v>6.5</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="52">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="50">
         <v>2</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="40">
         <v>12.19</v>
       </c>
       <c r="S5" s="41">
         <v>20.06</v>
       </c>
-      <c r="T5" s="47">
-        <v>26.31</v>
+      <c r="T5" s="46">
+        <v>28.56</v>
       </c>
     </row>
     <row r="6">
@@ -5490,7 +5522,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5505,41 +5537,41 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="54">
         <v>9.1</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="58">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="61">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="55">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="62">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="63">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="59">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="56">
         <v>-18.71</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="64">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="60">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="57">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="54">
-        <v>-38.6</v>
+      <c r="T6" s="65">
+        <v>-36.58</v>
       </c>
     </row>
     <row r="7">
@@ -5552,7 +5584,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5567,41 +5599,41 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="77">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="78">
         <v>0.95</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="68">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="73">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="74">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="69">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="75">
         <v>-6.98</v>
       </c>
       <c r="P7" s="71">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="76">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="70">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="72">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="68">
-        <v>-30.62</v>
+      <c r="T7" s="66">
+        <v>-28.34</v>
       </c>
     </row>
     <row r="8">
@@ -5614,7 +5646,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="81" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5629,41 +5661,41 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="82">
         <v>3.82</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="91">
         <v>14.19</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="87">
         <v>25.58</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="83">
         <v>38.12</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="88">
         <v>24.33</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="84">
         <v>11.91</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="89">
         <v>0.74</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="79">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="80">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="85">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="86">
         <v>-10.43</v>
       </c>
       <c r="T8" s="90">
-        <v>30.66</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="9">
@@ -5676,7 +5708,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="101" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5691,34 +5723,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="92">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="99">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="100">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="93">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="94">
         <v>-36.12</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="96">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="95">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="97">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="100">
+      <c r="T9" s="98">
         <v>-37.12</v>
       </c>
     </row>
@@ -5732,7 +5764,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="103" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5747,32 +5779,32 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="104">
+      <c r="I10" s="107">
         <v>-2.09</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="108">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="102">
         <v>-6</v>
       </c>
       <c r="L10" s="110">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="103">
         <v>-9.74</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="104">
         <v>-8.97</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="105">
         <v>-10.07</v>
       </c>
       <c r="P10" t="str"/>
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="102">
+      <c r="T10" s="106">
         <v>-10.07</v>
       </c>
     </row>
@@ -5786,7 +5818,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="118" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5801,41 +5833,41 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="117">
+      <c r="I11" s="119">
         <v>0</v>
       </c>
-      <c r="J11" s="113">
+      <c r="J11" s="120">
         <v>10</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="115">
         <v>21</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="111">
         <v>33.11</v>
       </c>
-      <c r="M11" s="114">
+      <c r="M11" s="112">
         <v>24.68</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="116">
         <v>37.11</v>
       </c>
-      <c r="O11" s="115">
+      <c r="O11" s="121">
         <v>50.84</v>
       </c>
-      <c r="P11" s="111">
+      <c r="P11" s="113">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="118">
+      <c r="Q11" s="122">
         <v>77.16</v>
       </c>
-      <c r="R11" s="116">
+      <c r="R11" s="114">
         <v>59.42</v>
       </c>
-      <c r="S11" s="112">
+      <c r="S11" s="123">
         <v>50.05</v>
       </c>
-      <c r="T11" s="119">
-        <v>54.84</v>
+      <c r="T11" s="117">
+        <v>57.84</v>
       </c>
     </row>
     <row r="12">
@@ -5848,7 +5880,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="124" t="str">
+      <c r="D12" s="126" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5863,41 +5895,41 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="133">
         <v>8.55</v>
       </c>
-      <c r="J12" s="129">
+      <c r="J12" s="127">
         <v>19.41</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="134">
         <v>11.85</v>
       </c>
-      <c r="L12" s="125">
+      <c r="L12" s="128">
         <v>22.99</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="135">
         <v>35.32</v>
       </c>
-      <c r="N12" s="133">
+      <c r="N12" s="130">
         <v>44.48</v>
       </c>
-      <c r="O12" s="126">
+      <c r="O12" s="124">
         <v>58.92</v>
       </c>
-      <c r="P12" s="127">
+      <c r="P12" s="131">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="132">
         <v>34.61</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="125">
         <v>45.23</v>
       </c>
-      <c r="S12" s="128">
+      <c r="S12" s="136">
         <v>42.21</v>
       </c>
-      <c r="T12" s="130">
-        <v>38.9</v>
+      <c r="T12" s="129">
+        <v>41.6</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +5942,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="142" t="str">
+      <c r="D13" s="147" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5925,41 +5957,41 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="137">
+      <c r="I13" s="148">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="143">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="138">
+      <c r="K13" s="144">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="138">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="140">
+      <c r="M13" s="139">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="140">
         <v>-1.22</v>
       </c>
-      <c r="O13" s="143">
+      <c r="O13" s="146">
         <v>-4.31</v>
       </c>
       <c r="P13" s="141">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="149">
         <v>33.43</v>
       </c>
       <c r="R13" s="145">
         <v>31.11</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="142">
         <v>64.98</v>
       </c>
-      <c r="T13" s="149">
-        <v>2.53</v>
+      <c r="T13" s="137">
+        <v>1.57</v>
       </c>
     </row>
     <row r="14">
@@ -5972,7 +6004,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="155" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -5987,41 +6019,41 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="156">
+      <c r="I14" s="151">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="150">
+      <c r="J14" s="152">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="161">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="153">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="151">
+      <c r="M14" s="162">
         <v>4.78</v>
       </c>
-      <c r="N14" s="152">
+      <c r="N14" s="156">
         <v>1.5</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="154">
         <v>27.74</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="159">
         <v>41.52</v>
       </c>
-      <c r="Q14" s="153">
+      <c r="Q14" s="157">
         <v>39.07</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="150">
         <v>75</v>
       </c>
-      <c r="S14" s="154">
+      <c r="S14" s="155">
         <v>60.1</v>
       </c>
-      <c r="T14" s="162">
-        <v>8.75</v>
+      <c r="T14" s="160">
+        <v>7.74</v>
       </c>
     </row>
     <row r="15">
@@ -6034,7 +6066,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="164" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6049,41 +6081,41 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="172">
+      <c r="I15" s="173">
         <v>-3.98</v>
       </c>
       <c r="J15" s="165">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="166">
+      <c r="K15" s="168">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="167">
+      <c r="L15" s="169">
         <v>7.16</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="166">
         <v>3.81</v>
       </c>
-      <c r="N15" s="163">
+      <c r="N15" s="167">
         <v>30.65</v>
       </c>
-      <c r="O15" s="168">
+      <c r="O15" s="170">
         <v>44.75</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="171">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="169">
+      <c r="Q15" s="174">
         <v>78.98</v>
       </c>
       <c r="R15" s="175">
         <v>63.75</v>
       </c>
-      <c r="S15" s="164">
+      <c r="S15" s="163">
         <v>56.8</v>
       </c>
-      <c r="T15" s="170">
-        <v>11.23</v>
+      <c r="T15" s="172">
+        <v>10.19</v>
       </c>
     </row>
     <row r="16">
@@ -6111,41 +6143,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="182">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="178">
+      <c r="J16" s="183">
         <v>-4.7</v>
       </c>
-      <c r="K16" s="180">
+      <c r="K16" s="186">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="178">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="187">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="181">
+      <c r="N16" s="188">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="176">
+      <c r="O16" s="184">
         <v>8.25</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="179">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="182">
+      <c r="Q16" s="176">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="179">
+      <c r="R16" s="180">
         <v>-5.62</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="185">
         <v>9.38</v>
       </c>
-      <c r="T16" s="187">
-        <v>-29.07</v>
+      <c r="T16" s="181">
+        <v>-29.73</v>
       </c>
     </row>
     <row r="17">
@@ -6158,7 +6190,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="190" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6173,41 +6205,41 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="192">
         <v>3.38</v>
       </c>
-      <c r="J17" s="193">
+      <c r="J17" s="195">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="193">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="189">
+      <c r="L17" s="194">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="200">
         <v>2.69</v>
       </c>
-      <c r="N17" s="194">
+      <c r="N17" s="196">
         <v>17.43</v>
       </c>
-      <c r="O17" s="191">
+      <c r="O17" s="198">
         <v>21.27</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="201">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="195">
+      <c r="Q17" s="189">
         <v>2.39</v>
       </c>
-      <c r="R17" s="192">
+      <c r="R17" s="190">
         <v>18.66</v>
       </c>
-      <c r="S17" s="196">
+      <c r="S17" s="199">
         <v>13.27</v>
       </c>
-      <c r="T17" s="200">
-        <v>-23.05</v>
+      <c r="T17" s="191">
+        <v>-23.76</v>
       </c>
     </row>
     <row r="18">
@@ -6220,7 +6252,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="213" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6235,41 +6267,41 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="205">
+      <c r="I18" s="214">
         <v>0</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="205">
         <v>9.99</v>
       </c>
-      <c r="K18" s="206">
+      <c r="K18" s="209">
         <v>20.99</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="202">
         <v>33.11</v>
       </c>
-      <c r="M18" s="202">
+      <c r="M18" s="210">
         <v>19.81</v>
       </c>
-      <c r="N18" s="207">
+      <c r="N18" s="203">
         <v>7.83</v>
       </c>
-      <c r="O18" s="208">
+      <c r="O18" s="211">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="206">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="207">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="208">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="203">
+      <c r="S18" s="204">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="204">
-        <v>-23.59</v>
+      <c r="T18" s="212">
+        <v>-25.55</v>
       </c>
     </row>
     <row r="19">
@@ -6282,7 +6314,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="219" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6297,25 +6329,25 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="219">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="215">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="223">
         <v>-7.41</v>
       </c>
-      <c r="L19" s="215">
+      <c r="L19" s="226">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="216">
         <v>-9.01</v>
       </c>
-      <c r="N19" s="216">
+      <c r="N19" s="220">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="220">
+      <c r="O19" s="227">
         <v>-8.21</v>
       </c>
       <c r="P19" s="221">
@@ -6324,14 +6356,14 @@
       <c r="Q19" s="217">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="224">
         <v>-11.35</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="218">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="223">
-        <v>-26.5</v>
+      <c r="T19" s="225">
+        <v>-26.2</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +6376,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="231" t="str">
+      <c r="D20" s="233" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6365,35 +6397,35 @@
       <c r="J20" s="229">
         <v>10.28</v>
       </c>
-      <c r="K20" s="232">
+      <c r="K20" s="236">
         <v>2.56</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="230">
         <v>11.62</v>
       </c>
-      <c r="M20" s="233">
+      <c r="M20" s="237">
         <v>10.45</v>
       </c>
-      <c r="N20" s="230">
+      <c r="N20" s="234">
         <v>8.02</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="235">
         <v>8.38</v>
       </c>
-      <c r="P20" s="234">
+      <c r="P20" s="238">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="231">
         <v>1.95</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="239">
         <v>28.49</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="240">
         <v>20.94</v>
       </c>
-      <c r="T20" s="240">
-        <v>20.12</v>
+      <c r="T20" s="232">
+        <v>17.62</v>
       </c>
     </row>
     <row r="21">
@@ -6406,7 +6438,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="249" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6421,41 +6453,41 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="245">
+      <c r="I21" s="250">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="243">
+      <c r="J21" s="251">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="247">
+      <c r="K21" s="252">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="244">
+      <c r="L21" s="241">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="246">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="248">
+      <c r="N21" s="242">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="244">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="246">
+      <c r="P21" s="243">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="247">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="241">
+      <c r="R21" s="253">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="242">
+      <c r="S21" s="248">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="250">
-        <v>-19.76</v>
+      <c r="T21" s="245">
+        <v>-18.27</v>
       </c>
     </row>
     <row r="22">
@@ -6468,7 +6500,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="265" t="str">
+      <c r="D22" s="263" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6483,41 +6515,41 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="264">
         <v>-2.78</v>
       </c>
-      <c r="J22" s="256">
+      <c r="J22" s="265">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="262">
+      <c r="K22" s="266">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="258">
+      <c r="L22" s="254">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="255">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="254">
+      <c r="N22" s="259">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="255">
+      <c r="O22" s="257">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="259">
+      <c r="P22" s="258">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="260">
+      <c r="Q22" s="256">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="260">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="257">
+      <c r="S22" s="261">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="264">
-        <v>-33.51</v>
+      <c r="T22" s="262">
+        <v>-36.09</v>
       </c>
     </row>
     <row r="23">
@@ -6530,7 +6562,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="268" t="str">
+      <c r="D23" s="274" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6545,94 +6577,86 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="276">
+      <c r="I23" s="275">
         <v>-6.44</v>
       </c>
-      <c r="J23" s="269">
+      <c r="J23" s="267">
         <v>-9.06</v>
       </c>
-      <c r="K23" s="270">
+      <c r="K23" s="276">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="271">
+      <c r="L23" s="270">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="272">
+      <c r="M23" s="271">
         <v>-10.99</v>
       </c>
       <c r="N23" s="277">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="268">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="273">
+      <c r="P23" s="278">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="272">
         <v>-10.03</v>
       </c>
       <c r="R23" s="279">
         <v>-10.32</v>
       </c>
-      <c r="S23" s="275">
+      <c r="S23" s="269">
         <v>-9.91</v>
       </c>
-      <c r="T23" s="267">
-        <v>-7.33</v>
+      <c r="T23" s="273">
+        <v>-5.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B24" t="str"/>
-      <c r="C24" t="str"/>
-      <c r="D24" t="str"/>
-      <c r="E24" t="str"/>
-      <c r="F24" t="str"/>
-      <c r="G24" t="str"/>
-      <c r="H24" t="str"/>
-      <c r="I24">
-        <v>22</v>
-      </c>
-      <c r="J24">
-        <v>22</v>
-      </c>
-      <c r="K24">
-        <v>22</v>
-      </c>
-      <c r="L24">
-        <v>22</v>
-      </c>
-      <c r="M24">
-        <v>22</v>
-      </c>
-      <c r="N24">
-        <v>22</v>
-      </c>
-      <c r="O24">
-        <v>22</v>
-      </c>
-      <c r="P24">
-        <v>21</v>
-      </c>
-      <c r="Q24">
-        <v>20</v>
-      </c>
-      <c r="R24">
-        <v>20</v>
-      </c>
-      <c r="S24">
-        <v>20</v>
-      </c>
-      <c r="T24">
-        <v>22</v>
-      </c>
+        <v>2026-04-27</v>
+      </c>
+      <c r="B24" t="str">
+        <v>鸿仕达</v>
+      </c>
+      <c r="C24" t="str">
+        <v>920125</v>
+      </c>
+      <c r="D24" s="281" t="str">
+        <v>净卖: -847.86万</v>
+      </c>
+      <c r="E24">
+        <v>48.58</v>
+      </c>
+      <c r="F24">
+        <v>53.82</v>
+      </c>
+      <c r="G24">
+        <v>48.58</v>
+      </c>
+      <c r="H24">
+        <v>-2.88</v>
+      </c>
+      <c r="I24" s="280">
+        <v>10.79</v>
+      </c>
+      <c r="J24" t="str"/>
+      <c r="K24" t="str"/>
+      <c r="L24" t="str"/>
+      <c r="M24" t="str"/>
+      <c r="N24" t="str"/>
+      <c r="O24" t="str"/>
+      <c r="P24" t="str"/>
+      <c r="Q24" t="str"/>
+      <c r="R24" t="str"/>
+      <c r="S24" t="str"/>
+      <c r="T24" t="str"/>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B25" t="str"/>
       <c r="C25" t="str"/>
@@ -6641,46 +6665,46 @@
       <c r="F25" t="str"/>
       <c r="G25" t="str"/>
       <c r="H25" t="str"/>
-      <c r="I25" s="288">
-        <v>27.27</v>
-      </c>
-      <c r="J25" s="289">
-        <v>45.45</v>
-      </c>
-      <c r="K25" s="286">
-        <v>31.82</v>
-      </c>
-      <c r="L25" s="287">
-        <v>40.91</v>
-      </c>
-      <c r="M25" s="290">
-        <v>40.91</v>
-      </c>
-      <c r="N25" s="281">
-        <v>40.91</v>
-      </c>
-      <c r="O25" s="282">
-        <v>40.91</v>
-      </c>
-      <c r="P25" s="291">
-        <v>47.62</v>
-      </c>
-      <c r="Q25" s="284">
-        <v>40</v>
-      </c>
-      <c r="R25" s="285">
-        <v>40</v>
-      </c>
-      <c r="S25" s="283">
-        <v>45</v>
-      </c>
-      <c r="T25" s="280">
-        <v>36.36</v>
+      <c r="I25">
+        <v>23</v>
+      </c>
+      <c r="J25">
+        <v>22</v>
+      </c>
+      <c r="K25">
+        <v>22</v>
+      </c>
+      <c r="L25">
+        <v>22</v>
+      </c>
+      <c r="M25">
+        <v>22</v>
+      </c>
+      <c r="N25">
+        <v>22</v>
+      </c>
+      <c r="O25">
+        <v>22</v>
+      </c>
+      <c r="P25">
+        <v>21</v>
+      </c>
+      <c r="Q25">
+        <v>20</v>
+      </c>
+      <c r="R25">
+        <v>20</v>
+      </c>
+      <c r="S25">
+        <v>20</v>
+      </c>
+      <c r="T25">
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B26" t="str"/>
       <c r="C26" t="str"/>
@@ -6689,41 +6713,89 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="294">
-        <v>-1.94</v>
-      </c>
-      <c r="J26" s="295">
+      <c r="I26" s="286">
+        <v>30.43</v>
+      </c>
+      <c r="J26" s="293">
+        <v>45.45</v>
+      </c>
+      <c r="K26" s="287">
+        <v>31.82</v>
+      </c>
+      <c r="L26" s="284">
+        <v>40.91</v>
+      </c>
+      <c r="M26" s="288">
+        <v>40.91</v>
+      </c>
+      <c r="N26" s="289">
+        <v>40.91</v>
+      </c>
+      <c r="O26" s="282">
+        <v>40.91</v>
+      </c>
+      <c r="P26" s="290">
+        <v>47.62</v>
+      </c>
+      <c r="Q26" s="291">
+        <v>40</v>
+      </c>
+      <c r="R26" s="283">
+        <v>40</v>
+      </c>
+      <c r="S26" s="285">
+        <v>45</v>
+      </c>
+      <c r="T26" s="292">
+        <v>36.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B27" t="str"/>
+      <c r="C27" t="str"/>
+      <c r="D27" t="str"/>
+      <c r="E27" t="str"/>
+      <c r="F27" t="str"/>
+      <c r="G27" t="str"/>
+      <c r="H27" t="str"/>
+      <c r="I27" s="304">
+        <v>-1.39</v>
+      </c>
+      <c r="J27" s="305">
         <v>-0.87</v>
       </c>
-      <c r="K26" s="303">
+      <c r="K27" s="299">
         <v>-1.81</v>
       </c>
-      <c r="L26" s="296">
+      <c r="L27" s="301">
         <v>-0.48</v>
       </c>
-      <c r="M26" s="298">
+      <c r="M27" s="294">
         <v>-2.06</v>
       </c>
-      <c r="N26" s="299">
+      <c r="N27" s="295">
         <v>-1.1</v>
       </c>
-      <c r="O26" s="297">
+      <c r="O27" s="300">
         <v>1.67</v>
       </c>
-      <c r="P26" s="292">
+      <c r="P27" s="302">
         <v>1.49</v>
       </c>
-      <c r="Q26" s="300">
+      <c r="Q27" s="303">
         <v>4.66</v>
       </c>
-      <c r="R26" s="293">
+      <c r="R27" s="296">
         <v>7.06</v>
       </c>
-      <c r="S26" s="301">
+      <c r="S27" s="297">
         <v>7.81</v>
       </c>
-      <c r="T26" s="302">
-        <v>-7.47</v>
+      <c r="T27" s="298">
+        <v>-6.93</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/涅盘重升/index.xlsx
+++ b/youzi/涅盘重升/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="307">
+  <fills count="309">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF32AB4D"/>
         <bgColor/>
       </patternFill>
@@ -69,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,19 +117,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,163 +195,1615 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0EBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1B7632"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,25 +1815,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3C"/>
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,1531 +1869,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D8DB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1843,32 +1879,22 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="306">
+  <borders count="308">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -4015,7 +4041,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="306">
+  <cellXfs count="308">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -4930,6 +4956,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="305" fillId="306" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="306" fillId="307" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="307" fillId="308" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -5289,41 +5321,41 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="3">
         <v>10.01</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="13">
         <v>17.19</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="4">
         <v>5.47</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="8">
         <v>-4.76</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="5">
         <v>-12.03</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="1">
         <v>-11.07</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="9">
         <v>-14.19</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="10">
         <v>-11.9</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="6">
         <v>-16.59</v>
       </c>
       <c r="S2" s="11">
         <v>-15.48</v>
       </c>
-      <c r="T2" s="4">
-        <v>-39.45</v>
+      <c r="T2" s="2">
+        <v>-41.29</v>
       </c>
     </row>
     <row r="3">
@@ -5336,7 +5368,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 2094.47万</v>
       </c>
       <c r="E3">
@@ -5351,41 +5383,41 @@
       <c r="H3">
         <v>-2.24</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="14">
         <v>7.24</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="22">
         <v>4.08</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="23">
         <v>-1.56</v>
       </c>
       <c r="L3" s="24">
         <v>0.96</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="19">
         <v>-9.12</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="15">
         <v>-11</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="21">
         <v>-8.43</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="25">
         <v>-12.88</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="20">
         <v>-16.36</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="16">
         <v>-15.44</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="17">
         <v>-14.94</v>
       </c>
-      <c r="T3" s="25">
-        <v>-9.9</v>
+      <c r="T3" s="18">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="4">
@@ -5398,7 +5430,7 @@
       <c r="C4" t="str">
         <v>600463</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 421.45万</v>
       </c>
       <c r="E4">
@@ -5413,41 +5445,41 @@
       <c r="H4">
         <v>10.04</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="33">
         <v>0</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="34">
         <v>0.15</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="39">
         <v>-9.89</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="28">
         <v>-18.33</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="37">
         <v>-20.71</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="29">
         <v>-21.78</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="35">
         <v>-21.93</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="30">
         <v>-23.39</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="36">
         <v>-23.47</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="27">
         <v>-22.78</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="31">
         <v>-22.55</v>
       </c>
-      <c r="T4" s="34">
-        <v>-20.78</v>
+      <c r="T4" s="38">
+        <v>-20.02</v>
       </c>
     </row>
     <row r="5">
@@ -5460,7 +5492,7 @@
       <c r="C5" t="str">
         <v>600513</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -610.16万</v>
       </c>
       <c r="E5">
@@ -5475,40 +5507,40 @@
       <c r="H5">
         <v>-2.91</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="45">
         <v>-7.31</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="43">
         <v>1.94</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="50">
         <v>4</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="51">
         <v>4.69</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="47">
         <v>11.75</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <v>4.44</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="52">
         <v>6.5</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="40">
         <v>5.56</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="46">
         <v>2</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="41">
         <v>12.19</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="42">
         <v>20.06</v>
       </c>
-      <c r="T5" s="46">
+      <c r="T5" s="49">
         <v>28.56</v>
       </c>
     </row>
@@ -5522,7 +5554,7 @@
       <c r="C6" t="str">
         <v>002883</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="62" t="str">
         <v>净买: 951.15万</v>
       </c>
       <c r="E6">
@@ -5537,41 +5569,41 @@
       <c r="H6">
         <v>0.85</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="55">
         <v>9.1</v>
       </c>
       <c r="J6" s="58">
         <v>-1.82</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="56">
         <v>-11.63</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="59">
         <v>-10.66</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <v>-13.91</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="60">
         <v>-17.61</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="64">
         <v>-17.67</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="61">
         <v>-18.71</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="65">
         <v>-17.67</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="53">
         <v>-18.78</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="54">
         <v>-19.1</v>
       </c>
-      <c r="T6" s="65">
-        <v>-36.58</v>
+      <c r="T6" s="57">
+        <v>-36.45</v>
       </c>
     </row>
     <row r="7">
@@ -5584,7 +5616,7 @@
       <c r="C7" t="str">
         <v>002883</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -786.72万</v>
       </c>
       <c r="E7">
@@ -5599,41 +5631,41 @@
       <c r="H7">
         <v>-9.86</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="78">
         <v>-0.15</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="73">
         <v>0.95</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="70">
         <v>-2.72</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="71">
         <v>-6.9</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="66">
         <v>-6.98</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="67">
         <v>-8.15</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="72">
         <v>-6.98</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="68">
         <v>-8.22</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="69">
         <v>-8.59</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="76">
         <v>-7.34</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="74">
         <v>-6.61</v>
       </c>
-      <c r="T7" s="66">
-        <v>-28.34</v>
+      <c r="T7" s="75">
+        <v>-28.19</v>
       </c>
     </row>
     <row r="8">
@@ -5646,7 +5678,7 @@
       <c r="C8" t="str">
         <v>605303</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 798.30万</v>
       </c>
       <c r="E8">
@@ -5661,41 +5693,41 @@
       <c r="H8">
         <v>5.98</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="81">
         <v>3.82</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="84">
         <v>14.19</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="90">
         <v>25.58</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="86">
         <v>38.12</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="87">
         <v>24.33</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="82">
         <v>11.91</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="88">
         <v>0.74</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="83">
         <v>2.28</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="91">
         <v>-4.73</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="79">
         <v>-9.17</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="89">
         <v>-10.43</v>
       </c>
-      <c r="T8" s="90">
-        <v>29.91</v>
+      <c r="T8" s="85">
+        <v>31.34</v>
       </c>
     </row>
     <row r="9">
@@ -5708,7 +5740,7 @@
       <c r="C9" t="str">
         <v>831834</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 619.11万</v>
       </c>
       <c r="E9">
@@ -5723,34 +5755,34 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="96">
         <v>-26.15</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <v>-31.54</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="101">
         <v>-33.27</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="94">
         <v>-34.27</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="92">
         <v>-36.12</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="95">
         <v>-36.88</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="97">
         <v>-36.35</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="98">
         <v>-37.12</v>
       </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="98">
+      <c r="T9" s="99">
         <v>-37.12</v>
       </c>
     </row>
@@ -5764,7 +5796,7 @@
       <c r="C10" t="str">
         <v>831834</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="107" t="str">
         <v>净卖: -480.48万</v>
       </c>
       <c r="E10">
@@ -5779,19 +5811,19 @@
       <c r="H10">
         <v>-5.31</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="102">
         <v>-2.09</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="106">
         <v>-4.57</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="103">
         <v>-6</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="108">
         <v>-8.64</v>
       </c>
-      <c r="M10" s="103">
+      <c r="M10" s="109">
         <v>-9.74</v>
       </c>
       <c r="N10" s="104">
@@ -5804,7 +5836,7 @@
       <c r="Q10" t="str"/>
       <c r="R10" t="str"/>
       <c r="S10" t="str"/>
-      <c r="T10" s="106">
+      <c r="T10" s="110">
         <v>-10.07</v>
       </c>
     </row>
@@ -5818,7 +5850,7 @@
       <c r="C11" t="str">
         <v>603216</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="122" t="str">
         <v>净买: 205.17万</v>
       </c>
       <c r="E11">
@@ -5833,7 +5865,7 @@
       <c r="H11">
         <v>10.02</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="114">
         <v>0</v>
       </c>
       <c r="J11" s="120">
@@ -5842,32 +5874,32 @@
       <c r="K11" s="115">
         <v>21</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="116">
         <v>33.11</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="123">
         <v>24.68</v>
       </c>
-      <c r="N11" s="116">
+      <c r="N11" s="117">
         <v>37.11</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="111">
         <v>50.84</v>
       </c>
-      <c r="P11" s="113">
+      <c r="P11" s="119">
         <v>61.05</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="121">
         <v>77.16</v>
       </c>
-      <c r="R11" s="114">
+      <c r="R11" s="112">
         <v>59.42</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="113">
         <v>50.05</v>
       </c>
-      <c r="T11" s="117">
-        <v>57.84</v>
+      <c r="T11" s="118">
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -5880,7 +5912,7 @@
       <c r="C12" t="str">
         <v>603216</v>
       </c>
-      <c r="D12" s="126" t="str">
+      <c r="D12" s="128" t="str">
         <v>净卖: -371.22万</v>
       </c>
       <c r="E12">
@@ -5895,41 +5927,41 @@
       <c r="H12">
         <v>1.34</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="132">
         <v>8.55</v>
       </c>
-      <c r="J12" s="127">
+      <c r="J12" s="136">
         <v>19.41</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="129">
         <v>11.85</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="131">
         <v>22.99</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="133">
         <v>35.32</v>
       </c>
-      <c r="N12" s="130">
+      <c r="N12" s="124">
         <v>44.48</v>
       </c>
-      <c r="O12" s="124">
+      <c r="O12" s="134">
         <v>58.92</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="125">
         <v>43.01</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="126">
         <v>34.61</v>
       </c>
-      <c r="R12" s="125">
+      <c r="R12" s="135">
         <v>45.23</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="127">
         <v>42.21</v>
       </c>
-      <c r="T12" s="129">
-        <v>41.6</v>
+      <c r="T12" s="130">
+        <v>39.05</v>
       </c>
     </row>
     <row r="13">
@@ -5942,7 +5974,7 @@
       <c r="C13" t="str">
         <v>920091</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="144" t="str">
         <v>净买: 395.40万</v>
       </c>
       <c r="E13">
@@ -5957,41 +5989,41 @@
       <c r="H13">
         <v>2.94</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="149">
         <v>-1.91</v>
       </c>
-      <c r="J13" s="143">
+      <c r="J13" s="139">
         <v>-8.92</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="147">
         <v>-11.5</v>
       </c>
-      <c r="L13" s="138">
+      <c r="L13" s="140">
         <v>-11.71</v>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="145">
         <v>-10.31</v>
       </c>
-      <c r="N13" s="140">
+      <c r="N13" s="148">
         <v>-1.22</v>
       </c>
       <c r="O13" s="146">
         <v>-4.31</v>
       </c>
-      <c r="P13" s="141">
+      <c r="P13" s="137">
         <v>20.43</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="141">
         <v>33.43</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="142">
         <v>31.11</v>
       </c>
-      <c r="S13" s="142">
+      <c r="S13" s="138">
         <v>64.98</v>
       </c>
-      <c r="T13" s="137">
-        <v>1.57</v>
+      <c r="T13" s="143">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="14">
@@ -6004,7 +6036,7 @@
       <c r="C14" t="str">
         <v>920091</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="153" t="str">
         <v>净卖: -26.55万</v>
       </c>
       <c r="E14">
@@ -6019,41 +6051,41 @@
       <c r="H14">
         <v>-3.89</v>
       </c>
-      <c r="I14" s="151">
+      <c r="I14" s="154">
         <v>-3.39</v>
       </c>
-      <c r="J14" s="152">
+      <c r="J14" s="162">
         <v>-6.12</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="150">
         <v>-6.35</v>
       </c>
-      <c r="L14" s="153">
+      <c r="L14" s="151">
         <v>-4.87</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="155">
         <v>4.78</v>
       </c>
       <c r="N14" s="156">
         <v>1.5</v>
       </c>
-      <c r="O14" s="154">
+      <c r="O14" s="152">
         <v>27.74</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="158">
         <v>41.52</v>
       </c>
       <c r="Q14" s="157">
         <v>39.07</v>
       </c>
-      <c r="R14" s="150">
+      <c r="R14" s="159">
         <v>75</v>
       </c>
-      <c r="S14" s="155">
+      <c r="S14" s="160">
         <v>60.1</v>
       </c>
-      <c r="T14" s="160">
-        <v>7.74</v>
+      <c r="T14" s="161">
+        <v>3.39</v>
       </c>
     </row>
     <row r="15">
@@ -6066,7 +6098,7 @@
       <c r="C15" t="str">
         <v>920091</v>
       </c>
-      <c r="D15" s="164" t="str">
+      <c r="D15" s="163" t="str">
         <v>净卖: -332.63万</v>
       </c>
       <c r="E15">
@@ -6081,41 +6113,41 @@
       <c r="H15">
         <v>1.2</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="164">
         <v>-3.98</v>
       </c>
-      <c r="J15" s="165">
+      <c r="J15" s="172">
         <v>-4.21</v>
       </c>
-      <c r="K15" s="168">
+      <c r="K15" s="169">
         <v>-2.7</v>
       </c>
-      <c r="L15" s="169">
+      <c r="L15" s="174">
         <v>7.16</v>
       </c>
-      <c r="M15" s="166">
+      <c r="M15" s="173">
         <v>3.81</v>
       </c>
-      <c r="N15" s="167">
+      <c r="N15" s="165">
         <v>30.65</v>
       </c>
       <c r="O15" s="170">
         <v>44.75</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="175">
         <v>42.24</v>
       </c>
-      <c r="Q15" s="174">
+      <c r="Q15" s="166">
         <v>78.98</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="171">
         <v>63.75</v>
       </c>
-      <c r="S15" s="163">
+      <c r="S15" s="167">
         <v>56.8</v>
       </c>
-      <c r="T15" s="172">
-        <v>10.19</v>
+      <c r="T15" s="168">
+        <v>5.75</v>
       </c>
     </row>
     <row r="16">
@@ -6128,7 +6160,7 @@
       <c r="C16" t="str">
         <v>920091</v>
       </c>
-      <c r="D16" s="177" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 676.85万</v>
       </c>
       <c r="E16">
@@ -6143,41 +6175,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="182">
+      <c r="I16" s="179">
         <v>-8.1</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="180">
         <v>-4.7</v>
       </c>
       <c r="K16" s="186">
         <v>-12.18</v>
       </c>
-      <c r="L16" s="178">
+      <c r="L16" s="177">
         <v>-10.93</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="181">
         <v>-13.5</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="182">
         <v>-5.34</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="183">
         <v>8.25</v>
       </c>
-      <c r="P16" s="179">
+      <c r="P16" s="187">
         <v>11.79</v>
       </c>
-      <c r="Q16" s="176">
+      <c r="Q16" s="184">
         <v>-2.26</v>
       </c>
-      <c r="R16" s="180">
+      <c r="R16" s="178">
         <v>-5.62</v>
       </c>
-      <c r="S16" s="185">
+      <c r="S16" s="188">
         <v>9.38</v>
       </c>
-      <c r="T16" s="181">
-        <v>-29.73</v>
+      <c r="T16" s="176">
+        <v>-32.56</v>
       </c>
     </row>
     <row r="17">
@@ -6190,7 +6222,7 @@
       <c r="C17" t="str">
         <v>920091</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="200" t="str">
         <v>净卖: -683.96万</v>
       </c>
       <c r="E17">
@@ -6205,41 +6237,41 @@
       <c r="H17">
         <v>0.31</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="196">
         <v>3.38</v>
       </c>
-      <c r="J17" s="195">
+      <c r="J17" s="201">
         <v>-4.73</v>
       </c>
-      <c r="K17" s="193">
+      <c r="K17" s="190">
         <v>-3.38</v>
       </c>
-      <c r="L17" s="194">
+      <c r="L17" s="191">
         <v>-6.16</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="189">
         <v>2.69</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="193">
         <v>17.43</v>
       </c>
-      <c r="O17" s="198">
+      <c r="O17" s="194">
         <v>21.27</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="192">
         <v>6.03</v>
       </c>
-      <c r="Q17" s="189">
+      <c r="Q17" s="197">
         <v>2.39</v>
       </c>
-      <c r="R17" s="190">
+      <c r="R17" s="198">
         <v>18.66</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="195">
         <v>13.27</v>
       </c>
-      <c r="T17" s="191">
-        <v>-23.76</v>
+      <c r="T17" s="199">
+        <v>-26.84</v>
       </c>
     </row>
     <row r="18">
@@ -6252,7 +6284,7 @@
       <c r="C18" t="str">
         <v>600783</v>
       </c>
-      <c r="D18" s="213" t="str">
+      <c r="D18" s="206" t="str">
         <v>净买: 1469.31万</v>
       </c>
       <c r="E18">
@@ -6267,41 +6299,41 @@
       <c r="H18">
         <v>9.99</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="202">
         <v>0</v>
       </c>
-      <c r="J18" s="205">
+      <c r="J18" s="212">
         <v>9.99</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="203">
         <v>20.99</v>
       </c>
-      <c r="L18" s="202">
+      <c r="L18" s="204">
         <v>33.11</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="213">
         <v>19.81</v>
       </c>
-      <c r="N18" s="203">
+      <c r="N18" s="205">
         <v>7.83</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="209">
         <v>-2.94</v>
       </c>
-      <c r="P18" s="206">
+      <c r="P18" s="207">
         <v>-12.22</v>
       </c>
-      <c r="Q18" s="207">
+      <c r="Q18" s="214">
         <v>-13.43</v>
       </c>
-      <c r="R18" s="208">
+      <c r="R18" s="210">
         <v>-17.28</v>
       </c>
-      <c r="S18" s="204">
+      <c r="S18" s="211">
         <v>-14.75</v>
       </c>
-      <c r="T18" s="212">
-        <v>-25.55</v>
+      <c r="T18" s="208">
+        <v>-29.13</v>
       </c>
     </row>
     <row r="19">
@@ -6314,7 +6346,7 @@
       <c r="C19" t="str">
         <v>920076</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="218" t="str">
         <v>净卖: -351.10万</v>
       </c>
       <c r="E19">
@@ -6329,41 +6361,41 @@
       <c r="H19">
         <v>-4.16</v>
       </c>
-      <c r="I19" s="219">
+      <c r="I19" s="223">
         <v>-2.85</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="227">
         <v>-4.56</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="219">
         <v>-7.41</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="224">
         <v>-8.43</v>
       </c>
-      <c r="M19" s="216">
+      <c r="M19" s="220">
         <v>-9.01</v>
       </c>
-      <c r="N19" s="220">
+      <c r="N19" s="221">
         <v>-8.25</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="225">
         <v>-8.21</v>
       </c>
-      <c r="P19" s="221">
+      <c r="P19" s="222">
         <v>-11.42</v>
       </c>
-      <c r="Q19" s="217">
+      <c r="Q19" s="215">
         <v>-11.5</v>
       </c>
-      <c r="R19" s="224">
+      <c r="R19" s="226">
         <v>-11.35</v>
       </c>
-      <c r="S19" s="218">
+      <c r="S19" s="216">
         <v>-13.43</v>
       </c>
-      <c r="T19" s="225">
-        <v>-26.2</v>
+      <c r="T19" s="217">
+        <v>-27.15</v>
       </c>
     </row>
     <row r="20">
@@ -6376,7 +6408,7 @@
       <c r="C20" t="str">
         <v>920088</v>
       </c>
-      <c r="D20" s="233" t="str">
+      <c r="D20" s="236" t="str">
         <v>净卖: -530.38万</v>
       </c>
       <c r="E20">
@@ -6391,41 +6423,41 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="228">
+      <c r="I20" s="240">
         <v>3.51</v>
       </c>
-      <c r="J20" s="229">
+      <c r="J20" s="228">
         <v>10.28</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="237">
         <v>2.56</v>
       </c>
-      <c r="L20" s="230">
+      <c r="L20" s="238">
         <v>11.62</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="229">
         <v>10.45</v>
       </c>
-      <c r="N20" s="234">
+      <c r="N20" s="239">
         <v>8.02</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="233">
         <v>8.38</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="234">
         <v>0.96</v>
       </c>
-      <c r="Q20" s="231">
+      <c r="Q20" s="230">
         <v>1.95</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="231">
         <v>28.49</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="235">
         <v>20.94</v>
       </c>
       <c r="T20" s="232">
-        <v>17.62</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="21">
@@ -6438,7 +6470,7 @@
       <c r="C21" t="str">
         <v>001260</v>
       </c>
-      <c r="D21" s="249" t="str">
+      <c r="D21" s="244" t="str">
         <v>净买: 602.19万</v>
       </c>
       <c r="E21">
@@ -6453,41 +6485,41 @@
       <c r="H21">
         <v>9.99</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="245">
         <v>-13.19</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="246">
         <v>-19.01</v>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="251">
         <v>-18.27</v>
       </c>
-      <c r="L21" s="241">
+      <c r="L21" s="247">
         <v>-19.2</v>
       </c>
-      <c r="M21" s="246">
+      <c r="M21" s="253">
         <v>-21.05</v>
       </c>
-      <c r="N21" s="242">
+      <c r="N21" s="248">
         <v>-23.72</v>
       </c>
-      <c r="O21" s="244">
+      <c r="O21" s="241">
         <v>-27.95</v>
       </c>
-      <c r="P21" s="243">
+      <c r="P21" s="242">
         <v>-24.31</v>
       </c>
-      <c r="Q21" s="247">
+      <c r="Q21" s="249">
         <v>-23.13</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="243">
         <v>-24.2</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="250">
         <v>-22.35</v>
       </c>
-      <c r="T21" s="245">
-        <v>-18.27</v>
+      <c r="T21" s="252">
+        <v>-18.38</v>
       </c>
     </row>
     <row r="22">
@@ -6500,7 +6532,7 @@
       <c r="C22" t="str">
         <v>301658</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="259" t="str">
         <v>净卖: -1206.79万</v>
       </c>
       <c r="E22">
@@ -6515,41 +6547,41 @@
       <c r="H22">
         <v>1.28</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="263">
         <v>-2.78</v>
       </c>
       <c r="J22" s="265">
         <v>-0.8</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="255">
         <v>-10.21</v>
       </c>
-      <c r="L22" s="254">
+      <c r="L22" s="256">
         <v>-15.88</v>
       </c>
-      <c r="M22" s="255">
+      <c r="M22" s="260">
         <v>-16.77</v>
       </c>
-      <c r="N22" s="259">
+      <c r="N22" s="257">
         <v>-22.88</v>
       </c>
-      <c r="O22" s="257">
+      <c r="O22" s="261">
         <v>-23.32</v>
       </c>
-      <c r="P22" s="258">
+      <c r="P22" s="266">
         <v>-29.39</v>
       </c>
-      <c r="Q22" s="256">
+      <c r="Q22" s="262">
         <v>-33.32</v>
       </c>
-      <c r="R22" s="260">
+      <c r="R22" s="254">
         <v>-33.76</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="264">
         <v>-32.07</v>
       </c>
-      <c r="T22" s="262">
-        <v>-36.09</v>
+      <c r="T22" s="258">
+        <v>-35.9</v>
       </c>
     </row>
     <row r="23">
@@ -6562,7 +6594,7 @@
       <c r="C23" t="str">
         <v>920188</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="278" t="str">
         <v>净卖: -506.29万</v>
       </c>
       <c r="E23">
@@ -6577,41 +6609,41 @@
       <c r="H23">
         <v>-10.5</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="279">
         <v>-6.44</v>
       </c>
       <c r="J23" s="267">
         <v>-9.06</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="270">
         <v>-5.96</v>
       </c>
-      <c r="L23" s="270">
+      <c r="L23" s="268">
         <v>-11.76</v>
       </c>
-      <c r="M23" s="271">
+      <c r="M23" s="274">
         <v>-10.99</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="275">
         <v>-9.66</v>
       </c>
-      <c r="O23" s="268">
+      <c r="O23" s="276">
         <v>-11.36</v>
       </c>
-      <c r="P23" s="278">
+      <c r="P23" s="269">
         <v>-11.69</v>
       </c>
-      <c r="Q23" s="272">
+      <c r="Q23" s="277">
         <v>-10.03</v>
       </c>
-      <c r="R23" s="279">
+      <c r="R23" s="271">
         <v>-10.32</v>
       </c>
-      <c r="S23" s="269">
+      <c r="S23" s="272">
         <v>-9.91</v>
       </c>
       <c r="T23" s="273">
-        <v>-5.7</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="24">
@@ -6624,7 +6656,7 @@
       <c r="C24" t="str">
         <v>920125</v>
       </c>
-      <c r="D24" s="281" t="str">
+      <c r="D24" s="283" t="str">
         <v>净卖: -847.86万</v>
       </c>
       <c r="E24">
@@ -6642,7 +6674,9 @@
       <c r="I24" s="280">
         <v>10.79</v>
       </c>
-      <c r="J24" t="str"/>
+      <c r="J24" s="281">
+        <v>6.22</v>
+      </c>
       <c r="K24" t="str"/>
       <c r="L24" t="str"/>
       <c r="M24" t="str"/>
@@ -6652,7 +6686,9 @@
       <c r="Q24" t="str"/>
       <c r="R24" t="str"/>
       <c r="S24" t="str"/>
-      <c r="T24" t="str"/>
+      <c r="T24" s="282">
+        <v>6.22</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -6669,7 +6705,7 @@
         <v>23</v>
       </c>
       <c r="J25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25">
         <v>22</v>
@@ -6699,7 +6735,7 @@
         <v>20</v>
       </c>
       <c r="T25">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -6713,41 +6749,41 @@
       <c r="F26" t="str"/>
       <c r="G26" t="str"/>
       <c r="H26" t="str"/>
-      <c r="I26" s="286">
+      <c r="I26" s="292">
         <v>30.43</v>
       </c>
-      <c r="J26" s="293">
-        <v>45.45</v>
-      </c>
-      <c r="K26" s="287">
+      <c r="J26" s="287">
+        <v>47.83</v>
+      </c>
+      <c r="K26" s="288">
         <v>31.82</v>
       </c>
-      <c r="L26" s="284">
+      <c r="L26" s="289">
         <v>40.91</v>
       </c>
-      <c r="M26" s="288">
+      <c r="M26" s="294">
         <v>40.91</v>
       </c>
-      <c r="N26" s="289">
+      <c r="N26" s="284">
         <v>40.91</v>
       </c>
-      <c r="O26" s="282">
+      <c r="O26" s="293">
         <v>40.91</v>
       </c>
       <c r="P26" s="290">
         <v>47.62</v>
       </c>
-      <c r="Q26" s="291">
+      <c r="Q26" s="295">
         <v>40</v>
       </c>
-      <c r="R26" s="283">
+      <c r="R26" s="291">
         <v>40</v>
       </c>
       <c r="S26" s="285">
         <v>45</v>
       </c>
-      <c r="T26" s="292">
-        <v>36.36</v>
+      <c r="T26" s="286">
+        <v>34.78</v>
       </c>
     </row>
     <row r="27">
@@ -6761,41 +6797,41 @@
       <c r="F27" t="str"/>
       <c r="G27" t="str"/>
       <c r="H27" t="str"/>
-      <c r="I27" s="304">
+      <c r="I27" s="301">
         <v>-1.39</v>
       </c>
-      <c r="J27" s="305">
-        <v>-0.87</v>
-      </c>
-      <c r="K27" s="299">
+      <c r="J27" s="299">
+        <v>-0.56</v>
+      </c>
+      <c r="K27" s="300">
         <v>-1.81</v>
       </c>
-      <c r="L27" s="301">
+      <c r="L27" s="307">
         <v>-0.48</v>
       </c>
-      <c r="M27" s="294">
+      <c r="M27" s="297">
         <v>-2.06</v>
       </c>
-      <c r="N27" s="295">
+      <c r="N27" s="302">
         <v>-1.1</v>
       </c>
-      <c r="O27" s="300">
+      <c r="O27" s="303">
         <v>1.67</v>
       </c>
-      <c r="P27" s="302">
+      <c r="P27" s="304">
         <v>1.49</v>
       </c>
-      <c r="Q27" s="303">
+      <c r="Q27" s="296">
         <v>4.66</v>
       </c>
-      <c r="R27" s="296">
+      <c r="R27" s="305">
         <v>7.06</v>
       </c>
-      <c r="S27" s="297">
+      <c r="S27" s="298">
         <v>7.81</v>
       </c>
-      <c r="T27" s="298">
-        <v>-6.93</v>
+      <c r="T27" s="306">
+        <v>-7.23</v>
       </c>
     </row>
   </sheetData>
